--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3285935D-95CF-4AD5-B1FE-40AB32625A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC73DFB3-A9CD-4EE6-A081-DCF47947ECC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
   <si>
     <t>firstletter</t>
   </si>
@@ -329,7 +329,39 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1565,10 +1597,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E2:AB2">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B4816EE8B5370BE58DA68AD559D404E83482B4A7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheetwithani" sheetId="3" r:id="rId1"/>
     <sheet name="conventions" sheetId="4" r:id="rId2"/>
     <sheet name="bad" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -436,7 +437,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -520,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -529,249 +530,31 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -853,6 +636,51 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1131,38 +959,38 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" customWidth="1"/>
-    <col min="2" max="2" width="4.08984375" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="7" style="14" customWidth="1"/>
-    <col min="6" max="6" width="20.36328125" customWidth="1"/>
-    <col min="7" max="7" width="12.7265625" customWidth="1"/>
-    <col min="8" max="15" width="7.08984375" customWidth="1"/>
-    <col min="16" max="16" width="30.81640625" customWidth="1"/>
-    <col min="17" max="17" width="15.1796875" customWidth="1"/>
-    <col min="18" max="18" width="12.1796875" customWidth="1"/>
-    <col min="19" max="19" width="15.1796875" customWidth="1"/>
-    <col min="20" max="20" width="15.36328125" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" customWidth="1"/>
+    <col min="5" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="15" width="7.109375" customWidth="1"/>
+    <col min="16" max="16" width="30.77734375" customWidth="1"/>
+    <col min="17" max="17" width="15.21875" customWidth="1"/>
+    <col min="18" max="18" width="12.21875" customWidth="1"/>
+    <col min="19" max="19" width="15.21875" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="H1" s="8" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="H1" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8" t="s">
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
       <c r="P1" t="s">
         <v>94</v>
       </c>
@@ -1173,7 +1001,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>119</v>
       </c>
@@ -1213,17 +1041,17 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" t="s">
         <v>111</v>
       </c>
       <c r="F3" t="s">
@@ -1264,7 +1092,7 @@
         <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','coolant','minerals','salvage','description'],</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>65</v>
       </c>
@@ -1275,10 +1103,10 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4">
         <v>15</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -1299,7 +1127,7 @@
         <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5">
         <f t="shared" ref="B5:B44" si="2">SUM(H5:O5)</f>
@@ -1308,10 +1136,10 @@
       <c r="C5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5">
         <v>8</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5">
         <v>10</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -1335,7 +1163,7 @@
         <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6">
         <f t="shared" si="2"/>
@@ -1344,10 +1172,10 @@
       <c r="C6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6">
         <v>12</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1371,7 +1199,7 @@
         <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7">
         <f t="shared" si="2"/>
@@ -1380,10 +1208,10 @@
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7">
         <v>10</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -1407,7 +1235,7 @@
         <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8">
         <f t="shared" si="2"/>
@@ -1416,10 +1244,10 @@
       <c r="C8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8">
         <v>13</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8">
         <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -1443,7 +1271,7 @@
         <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9">
         <f t="shared" si="2"/>
@@ -1452,10 +1280,10 @@
       <c r="C9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -1476,7 +1304,7 @@
         <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10">
         <f t="shared" si="2"/>
@@ -1485,10 +1313,10 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10">
         <v>11</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -1512,7 +1340,7 @@
         <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11">
         <f t="shared" si="2"/>
@@ -1521,10 +1349,10 @@
       <c r="C11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11">
         <v>13</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11">
         <v>20</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -1548,7 +1376,7 @@
         <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12">
         <f t="shared" si="2"/>
@@ -1557,10 +1385,10 @@
       <c r="C12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12">
         <v>14</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12">
         <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -1587,7 +1415,7 @@
         <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13">
         <f t="shared" si="2"/>
@@ -1596,10 +1424,10 @@
       <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13">
         <v>20</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13">
         <v>20</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -1626,8 +1454,8 @@
         <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0],</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B14">
@@ -1637,7 +1465,7 @@
       <c r="C14" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14">
         <v>30</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -1660,8 +1488,8 @@
         <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,0,0,'Allows you to explore space.'],</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="15"/>
       <c r="B15">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1669,23 +1497,23 @@
       <c r="C15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="P15" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="Q15" s="9"/>
+      <c r="Q15" s="8"/>
       <c r="T15" t="str">
         <f t="shared" si="1"/>
         <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,0,0,'Lets you peek into the endless void of space.'],</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
+    <row r="16" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
       <c r="B16">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1693,14 +1521,14 @@
       <c r="C16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
       <c r="R16" t="s">
         <v>81</v>
       </c>
@@ -1709,8 +1537,8 @@
         <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A17" s="11"/>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
       <c r="B17">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1718,21 +1546,21 @@
       <c r="C17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
       <c r="T17" t="str">
         <f t="shared" si="1"/>
         <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B18">
@@ -1742,10 +1570,10 @@
       <c r="C18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18">
         <v>5</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18">
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
@@ -1764,8 +1592,8 @@
         <v>['mining',5,30,'Mining station','CAPTURE',0,0,0,0,0,0,15,0,0],</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A19" s="10"/>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
       <c r="B19">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1773,10 +1601,10 @@
       <c r="C19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19">
         <v>5</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19">
         <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
@@ -1795,8 +1623,8 @@
         <v>['scrapyard',5,30,'Scrapyard','CAPTURE',0,0,0,0,0,0,0,15,0],</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A20" s="10"/>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
       <c r="B20">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1804,10 +1632,10 @@
       <c r="C20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20">
         <v>5</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20">
         <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
@@ -1832,8 +1660,8 @@
         <v>['data',5,30,'Data vault','CAPTURE',0,0,0,0,0,5,5,5,0],</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A21" s="10"/>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
       <c r="B21">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1841,10 +1669,10 @@
       <c r="C21" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21">
         <v>5</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21">
         <v>30</v>
       </c>
       <c r="F21" s="3" t="s">
@@ -1860,8 +1688,8 @@
         <v>['supply',5,30,'Supply depot','CAPTURE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A22" s="10"/>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="14"/>
       <c r="B22">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1869,10 +1697,10 @@
       <c r="C22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22">
         <v>5</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22">
         <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -1891,8 +1719,8 @@
         <v>['fusion',5,40,'Fusion core','CAPTURE',0,0,0,0,15,0,0,0,0],</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
       <c r="B23">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1900,10 +1728,10 @@
       <c r="C23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23">
         <v>5</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23">
         <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
@@ -1925,8 +1753,8 @@
         <v>['alloy',5,30,'Alloy plant','CAPTURE',0,0,0,0,0,0,10,5,0],</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A24" s="10"/>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="14"/>
       <c r="B24">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -1934,10 +1762,10 @@
       <c r="C24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24">
         <v>5</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24">
         <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1962,8 +1790,8 @@
         <v>['research',5,40,'Research lab','CAPTURE',0,0,0,0,5,5,0,5,0],</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A25" s="10"/>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
       <c r="B25">
         <f t="shared" si="2"/>
         <v>120</v>
@@ -1971,7 +1799,7 @@
       <c r="C25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25">
         <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
@@ -1986,8 +1814,8 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" s="14"/>
       <c r="B26">
         <f t="shared" si="2"/>
         <v>120</v>
@@ -1995,7 +1823,7 @@
       <c r="C26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26">
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
@@ -2010,8 +1838,8 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A27" s="10"/>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A27" s="14"/>
       <c r="B27">
         <f t="shared" si="2"/>
         <v>120</v>
@@ -2019,7 +1847,7 @@
       <c r="C27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27">
         <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
@@ -2034,8 +1862,8 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A28" s="10"/>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" s="14"/>
       <c r="B28">
         <f t="shared" si="2"/>
         <v>120</v>
@@ -2043,7 +1871,7 @@
       <c r="C28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28">
         <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -2058,8 +1886,8 @@
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A29" s="10"/>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" s="14"/>
       <c r="B29">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -2067,7 +1895,7 @@
       <c r="C29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29">
         <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
@@ -2086,8 +1914,8 @@
         <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0],</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A30" s="10"/>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A30" s="14"/>
       <c r="B30">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -2095,7 +1923,7 @@
       <c r="C30" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30">
         <v>40</v>
       </c>
       <c r="F30" s="3" t="s">
@@ -2114,8 +1942,8 @@
         <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0],</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A31" s="10"/>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A31" s="14"/>
       <c r="B31">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -2123,7 +1951,7 @@
       <c r="C31" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31">
         <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
@@ -2142,8 +1970,8 @@
         <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0],</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A32" s="10"/>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A32" s="14"/>
       <c r="B32">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -2151,7 +1979,7 @@
       <c r="C32" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32">
         <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
@@ -2170,8 +1998,8 @@
         <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0],</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A33" s="10"/>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A33" s="14"/>
       <c r="B33">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2179,7 +2007,7 @@
       <c r="C33" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33">
         <v>0</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -2195,8 +2023,8 @@
         <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A34" s="10"/>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A34" s="14"/>
       <c r="B34">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2204,7 +2032,7 @@
       <c r="C34" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34">
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
@@ -2220,8 +2048,8 @@
         <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A35" s="10"/>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A35" s="14"/>
       <c r="B35">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2229,7 +2057,7 @@
       <c r="C35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35">
         <v>50</v>
       </c>
       <c r="F35" s="3" t="s">
@@ -2245,8 +2073,8 @@
         <v>['door_hard',0,50,'High security door','HACK',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A36" s="10"/>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A36" s="14"/>
       <c r="B36">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -2260,7 +2088,7 @@
         <v>[0,0,0,0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>95</v>
       </c>
@@ -2268,153 +2096,153 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37">
         <v>10</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G37" t="s">
         <v>108</v>
       </c>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
       <c r="T37" t="str">
         <f t="shared" si="1"/>
         <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38">
         <v>10</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G38" t="s">
         <v>108</v>
       </c>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
       <c r="T38" t="str">
         <f t="shared" si="1"/>
         <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="F39" s="13"/>
+      <c r="C39" s="9"/>
+      <c r="F39" s="9"/>
       <c r="G39" t="s">
         <v>108</v>
       </c>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
       <c r="T39" t="str">
         <f t="shared" si="1"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
       <c r="B40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="F40" s="13"/>
+      <c r="C40" s="9"/>
+      <c r="F40" s="9"/>
       <c r="G40" t="s">
         <v>108</v>
       </c>
-      <c r="P40" s="13"/>
-      <c r="Q40" s="13"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
       <c r="T40" t="str">
         <f t="shared" si="1"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="12"/>
       <c r="B41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="C41" s="9"/>
+      <c r="F41" s="9"/>
       <c r="G41" t="s">
         <v>108</v>
       </c>
-      <c r="P41" s="13"/>
-      <c r="Q41" s="13"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
       <c r="T41" t="str">
         <f t="shared" si="1"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="12"/>
       <c r="B42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="C42" s="9"/>
+      <c r="F42" s="9"/>
       <c r="G42" t="s">
         <v>108</v>
       </c>
-      <c r="P42" s="13"/>
-      <c r="Q42" s="13"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
       <c r="T42" t="str">
         <f t="shared" si="1"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="C43" s="9"/>
+      <c r="F43" s="9"/>
       <c r="G43" t="s">
         <v>108</v>
       </c>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
       <c r="T43" t="str">
         <f t="shared" si="1"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="F44" s="13"/>
+      <c r="C44" s="9"/>
+      <c r="F44" s="9"/>
       <c r="G44" t="s">
         <v>108</v>
       </c>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="13"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
       <c r="T44" t="str">
         <f t="shared" si="1"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
@@ -2429,29 +2257,14 @@
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="A14:A17"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C17 C37:C1048576">
+    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D2:O2 T2:U2">
-    <cfRule type="duplicateValues" dxfId="16" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:S2">
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:R3">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C17 C37:C1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P37:Q44">
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37:F44">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E62">
     <cfRule type="colorScale" priority="2">
@@ -2465,8 +2278,23 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="F37:F44">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P37:Q44">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:R3">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:S2">
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2474,20 +2302,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="97.453125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="97.44140625" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="97.453125" style="15"/>
+    <col min="1" max="16384" width="97.44140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2497,17 +2325,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:Z31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="7.36328125" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" customWidth="1"/>
+    <col min="5" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -2579,7 +2407,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -2622,15 +2450,15 @@
       <c r="O3" t="s">
         <v>11</v>
       </c>
-      <c r="P3" t="e" cm="1">
-        <f t="array" aca="1" ref="P3" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D3:O3),""""&amp;D3:O3&amp;"""",IF(D3:O3="",0,D3:O3)))&amp;"],"</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B4" t="e">
-        <f ca="1">SUM(E4:AA4)</f>
-        <v>#NAME?</v>
+      <c r="P3" t="str" cm="1">
+        <f t="array" ref="P3">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D3:O3),""""&amp;D3:O3&amp;"""",IF(D3:O3="",0,D3:O3)))&amp;"],"</f>
+        <v>["terminal","delay","question","pretty","action","energy","food","water","parts","metals","titanium","alloy"],</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <f>SUM(E4:AA4)</f>
+        <v>55</v>
       </c>
       <c r="C4" t="str">
         <f>LEFT(D4,1)</f>
@@ -2654,15 +2482,15 @@
       <c r="I4">
         <v>40</v>
       </c>
-      <c r="P4" t="e" cm="1">
-        <f t="array" aca="1" ref="P4" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D4:O4),""""&amp;D4:O4&amp;"""",IF(D4:O4="",0,D4:O4)))&amp;"],"</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B5" t="e">
-        <f t="shared" ref="B5:B31" ca="1" si="1">SUM(E5:AA5)</f>
-        <v>#NAME?</v>
+      <c r="P4" t="str" cm="1">
+        <f t="array" ref="P4">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D4:O4),""""&amp;D4:O4&amp;"""",IF(D4:O4="",0,D4:O4)))&amp;"],"</f>
+        <v>["reactor",15,0,"Reactor","REPAIR",40,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <f t="shared" ref="B5:B31" si="1">SUM(E5:AA5)</f>
+        <v>55</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" ref="C5:C31" si="2">LEFT(D5,1)</f>
@@ -2686,19 +2514,19 @@
       <c r="I5">
         <v>25</v>
       </c>
-      <c r="P5" t="e" cm="1">
-        <f t="array" aca="1" ref="P5" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D5:O5),""""&amp;D5:O5&amp;"""",IF(D5:O5="",0,D5:O5)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P5" t="str" cm="1">
+        <f t="array" ref="P5">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D5:O5),""""&amp;D5:O5&amp;"""",IF(D5:O5="",0,D5:O5)))&amp;"],"</f>
+        <v>["solar",20,10,"Solar Array","REPAIR",25,0,0,0,0,0,0],</v>
       </c>
       <c r="S5" t="str">
         <f>" * @property {number} "&amp;D5</f>
         <v xml:space="preserve"> * @property {number} solar</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B6" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <f t="shared" si="1"/>
+        <v>57</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="2"/>
@@ -2725,19 +2553,19 @@
       <c r="K6">
         <v>10</v>
       </c>
-      <c r="P6" t="e" cm="1">
-        <f t="array" aca="1" ref="P6" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D6:O6),""""&amp;D6:O6&amp;"""",IF(D6:O6="",0,D6:O6)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P6" t="str" cm="1">
+        <f t="array" ref="P6">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D6:O6),""""&amp;D6:O6&amp;"""",IF(D6:O6="",0,D6:O6)))&amp;"],"</f>
+        <v>["hydro",12,20,"Hydroponics","REPAIR",0,15,10,0,0,0,0],</v>
       </c>
       <c r="S6" t="str">
         <f t="shared" ref="S6:S23" si="3">" * @property {number} "&amp;D6</f>
         <v xml:space="preserve"> * @property {number} hydro</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B7" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="2"/>
@@ -2761,19 +2589,19 @@
       <c r="K7">
         <v>25</v>
       </c>
-      <c r="P7" t="e" cm="1">
-        <f t="array" aca="1" ref="P7" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D7:O7),""""&amp;D7:O7&amp;"""",IF(D7:O7="",0,D7:O7)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P7" t="str" cm="1">
+        <f t="array" ref="P7">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D7:O7),""""&amp;D7:O7&amp;"""",IF(D7:O7="",0,D7:O7)))&amp;"],"</f>
+        <v>["water",10,20,"Water recycler","REPAIR",0,0,25,0,0,0,0],</v>
       </c>
       <c r="S7" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} water</v>
       </c>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B8" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <f t="shared" si="1"/>
+        <v>48</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="2"/>
@@ -2800,19 +2628,19 @@
       <c r="L8">
         <v>10</v>
       </c>
-      <c r="P8" t="e" cm="1">
-        <f t="array" aca="1" ref="P8" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D8:O8),""""&amp;D8:O8&amp;"""",IF(D8:O8="",0,D8:O8)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P8" t="str" cm="1">
+        <f t="array" ref="P8">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D8:O8),""""&amp;D8:O8&amp;"""",IF(D8:O8="",0,D8:O8)))&amp;"],"</f>
+        <v>["cargo",8,20,"Cargo bay","REPAIR",0,10,0,10,0,0,0],</v>
       </c>
       <c r="S8" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} cargo</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B9" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <f t="shared" si="1"/>
+        <v>92</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="2"/>
@@ -2836,19 +2664,19 @@
       <c r="L9">
         <v>30</v>
       </c>
-      <c r="P9" t="e" cm="1">
-        <f t="array" aca="1" ref="P9" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D9:O9),""""&amp;D9:O9&amp;"""",IF(D9:O9="",0,D9:O9)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P9" t="str" cm="1">
+        <f t="array" ref="P9">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D9:O9),""""&amp;D9:O9&amp;"""",IF(D9:O9="",0,D9:O9)))&amp;"],"</f>
+        <v>["comms",12,50,"Comms array","REPAIR",0,0,0,30,0,0,0],</v>
       </c>
       <c r="S9" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} comms</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B10" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <f t="shared" si="1"/>
+        <v>95</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="2"/>
@@ -2875,19 +2703,19 @@
       <c r="L10">
         <v>5</v>
       </c>
-      <c r="P10" t="e" cm="1">
-        <f t="array" aca="1" ref="P10" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D10:O10),""""&amp;D10:O10&amp;"""",IF(D10:O10="",0,D10:O10)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P10" t="str" cm="1">
+        <f t="array" ref="P10">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D10:O10),""""&amp;D10:O10&amp;"""",IF(D10:O10="",0,D10:O10)))&amp;"],"</f>
+        <v>["fab",10,60,"Fabricator","REPAIR",0,0,20,5,0,0,0],</v>
       </c>
       <c r="S10" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} fab</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B11" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="2"/>
@@ -2911,19 +2739,19 @@
       <c r="L11">
         <v>10</v>
       </c>
-      <c r="P11" t="e" cm="1">
-        <f t="array" aca="1" ref="P11" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D11:O11),""""&amp;D11:O11&amp;"""",IF(D11:O11="",0,D11:O11)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P11" t="str" cm="1">
+        <f t="array" ref="P11">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D11:O11),""""&amp;D11:O11&amp;"""",IF(D11:O11="",0,D11:O11)))&amp;"],"</f>
+        <v>["med",10,30,"Medical bay","REPAIR",0,0,0,10,0,0,0],</v>
       </c>
       <c r="S11" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} med</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B12" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="2"/>
@@ -2950,19 +2778,19 @@
       <c r="K12">
         <v>15</v>
       </c>
-      <c r="P12" t="e" cm="1">
-        <f t="array" aca="1" ref="P12" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D12:O12),""""&amp;D12:O12&amp;"""",IF(D12:O12="",0,D12:O12)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P12" t="str" cm="1">
+        <f t="array" ref="P12">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D12:O12),""""&amp;D12:O12&amp;"""",IF(D12:O12="",0,D12:O12)))&amp;"],"</f>
+        <v>["life",20,10,"Life support","REPAIR",0,10,15,0,0,0,0],</v>
       </c>
       <c r="S12" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} life</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
-      <c r="B13" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>87</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="2"/>
@@ -2986,16 +2814,16 @@
       <c r="K13">
         <v>25</v>
       </c>
-      <c r="P13" t="e" cm="1">
-        <f t="array" aca="1" ref="P13" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D13:O13),""""&amp;D13:O13&amp;"""",IF(D13:O13="",0,D13:O13)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P13" t="str" cm="1">
+        <f t="array" ref="P13">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D13:O13),""""&amp;D13:O13&amp;"""",IF(D13:O13="",0,D13:O13)))&amp;"],"</f>
+        <v>["machine",12,50,"Machine shop","REPAIR",0,0,25,0,0,0,0],</v>
       </c>
       <c r="S13" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} machine</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C14" t="str">
         <f t="shared" si="2"/>
         <v>s</v>
@@ -3009,16 +2837,16 @@
       <c r="H14" t="s">
         <v>37</v>
       </c>
-      <c r="P14" t="e" cm="1">
-        <f t="array" aca="1" ref="P14" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D14:O14),""""&amp;D14:O14&amp;"""",IF(D14:O14="",0,D14:O14)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P14" t="str" cm="1">
+        <f t="array" ref="P14">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D14:O14),""""&amp;D14:O14&amp;"""",IF(D14:O14="",0,D14:O14)))&amp;"],"</f>
+        <v>["shuttle",0,0,"Shuttle bay","USE",0,0,0,0,0,0,0],</v>
       </c>
       <c r="S14" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} shuttle</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f t="shared" si="2"/>
         <v>a</v>
@@ -3032,16 +2860,16 @@
       <c r="H15" t="s">
         <v>37</v>
       </c>
-      <c r="P15" t="e" cm="1">
-        <f t="array" aca="1" ref="P15" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D15:O15),""""&amp;D15:O15&amp;"""",IF(D15:O15="",0,D15:O15)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P15" t="str" cm="1">
+        <f t="array" ref="P15">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D15:O15),""""&amp;D15:O15&amp;"""",IF(D15:O15="",0,D15:O15)))&amp;"],"</f>
+        <v>["access",0,0,"Upgrade center","USE",0,0,0,0,0,0,0],</v>
       </c>
       <c r="S15" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} access</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f t="shared" si="2"/>
         <v>d</v>
@@ -3055,19 +2883,19 @@
       <c r="H16" t="s">
         <v>37</v>
       </c>
-      <c r="P16" t="e" cm="1">
-        <f t="array" aca="1" ref="P16" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D16:O16),""""&amp;D16:O16&amp;"""",IF(D16:O16="",0,D16:O16)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P16" t="str" cm="1">
+        <f t="array" ref="P16">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D16:O16),""""&amp;D16:O16&amp;"""",IF(D16:O16="",0,D16:O16)))&amp;"],"</f>
+        <v>["door",0,0,"ACCESS KEY NEEDED","USE",0,0,0,0,0,0,0],</v>
       </c>
       <c r="S16" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} door</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B17" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="2"/>
@@ -3097,19 +2925,19 @@
       <c r="N17">
         <v>5</v>
       </c>
-      <c r="P17" t="e" cm="1">
-        <f t="array" aca="1" ref="P17" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D17:O17),""""&amp;D17:O17&amp;"""",IF(D17:O17="",0,D17:O17)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P17" t="str" cm="1">
+        <f t="array" ref="P17">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D17:O17),""""&amp;D17:O17&amp;"""",IF(D17:O17="",0,D17:O17)))&amp;"],"</f>
+        <v>["mining",15,60,"Mining station","CAPTURE",10,0,0,0,10,5,0],</v>
       </c>
       <c r="S17" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} mining</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B18" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>75</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="2"/>
@@ -3136,19 +2964,19 @@
       <c r="N18">
         <v>10</v>
       </c>
-      <c r="P18" t="e" cm="1">
-        <f t="array" aca="1" ref="P18" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D18:O18),""""&amp;D18:O18&amp;"""",IF(D18:O18="",0,D18:O18)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P18" t="str" cm="1">
+        <f t="array" ref="P18">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D18:O18),""""&amp;D18:O18&amp;"""",IF(D18:O18="",0,D18:O18)))&amp;"],"</f>
+        <v>["scrapyard",10,40,"Scrapyard","CAPTURE",0,0,0,15,0,10,0],</v>
       </c>
       <c r="S18" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} scrapyard</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B19" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>127</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="2"/>
@@ -3181,19 +3009,19 @@
       <c r="O19">
         <v>5</v>
       </c>
-      <c r="P19" t="e" cm="1">
-        <f t="array" aca="1" ref="P19" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D19:O19),""""&amp;D19:O19&amp;"""",IF(D19:O19="",0,D19:O19)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P19" t="str" cm="1">
+        <f t="array" ref="P19">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D19:O19),""""&amp;D19:O19&amp;"""",IF(D19:O19="",0,D19:O19)))&amp;"],"</f>
+        <v>["data",12,70,"Data vault","CAPTURE",0,0,0,30,5,5,5],</v>
       </c>
       <c r="S19" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} data</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B20" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <f t="shared" si="1"/>
+        <v>125</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="2"/>
@@ -3223,19 +3051,19 @@
       <c r="O20">
         <v>5</v>
       </c>
-      <c r="P20" t="e" cm="1">
-        <f t="array" aca="1" ref="P20" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D20:O20),""""&amp;D20:O20&amp;"""",IF(D20:O20="",0,D20:O20)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P20" t="str" cm="1">
+        <f t="array" ref="P20">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D20:O20),""""&amp;D20:O20&amp;"""",IF(D20:O20="",0,D20:O20)))&amp;"],"</f>
+        <v>["supply",15,80,"Supply depot","CAPTURE",0,0,15,0,10,0,5],</v>
       </c>
       <c r="S20" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} supply</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B21" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <f t="shared" si="1"/>
+        <v>140</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="2"/>
@@ -3265,19 +3093,19 @@
       <c r="O21">
         <v>10</v>
       </c>
-      <c r="P21" t="e" cm="1">
-        <f t="array" aca="1" ref="P21" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D21:O21),""""&amp;D21:O21&amp;"""",IF(D21:O21="",0,D21:O21)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P21" t="str" cm="1">
+        <f t="array" ref="P21">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D21:O21),""""&amp;D21:O21&amp;"""",IF(D21:O21="",0,D21:O21)))&amp;"],"</f>
+        <v>["fusion",10,90,"Fusion core","CAPTURE",20,0,0,0,0,10,10],</v>
       </c>
       <c r="S21" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} fusion</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B22" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <f t="shared" si="1"/>
+        <v>170</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="2"/>
@@ -3304,19 +3132,19 @@
       <c r="M22">
         <v>20</v>
       </c>
-      <c r="P22" t="e" cm="1">
-        <f t="array" aca="1" ref="P22" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D22:O22),""""&amp;D22:O22&amp;"""",IF(D22:O22="",0,D22:O22)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P22" t="str" cm="1">
+        <f t="array" ref="P22">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D22:O22),""""&amp;D22:O22&amp;"""",IF(D22:O22="",0,D22:O22)))&amp;"],"</f>
+        <v>["alloy",20,100,"Alloy plant","CAPTURE",30,0,0,0,20,0,0],</v>
       </c>
       <c r="S22" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} alloy</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
-      <c r="B23" t="e">
-        <f t="shared" ca="1" si="1"/>
-        <v>#NAME?</v>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <f t="shared" si="1"/>
+        <v>127</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="2"/>
@@ -3346,16 +3174,16 @@
       <c r="O23">
         <v>5</v>
       </c>
-      <c r="P23" t="e" cm="1">
-        <f t="array" aca="1" ref="P23" ca="1">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D23:O23),""""&amp;D23:O23&amp;"""",IF(D23:O23="",0,D23:O23)))&amp;"],"</f>
-        <v>#NAME?</v>
+      <c r="P23" t="str" cm="1">
+        <f t="array" ref="P23">"["&amp;_xlfn.TEXTJOIN(",",FALSE,IF(ISTEXT(D23:O23),""""&amp;D23:O23&amp;"""",IF(D23:O23="",0,D23:O23)))&amp;"],"</f>
+        <v>["research",12,85,"Research lab","CAPTURE",10,0,0,0,0,15,5],</v>
       </c>
       <c r="S23" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve"> * @property {number} research</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3365,7 +3193,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3375,7 +3203,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3385,7 +3213,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3395,7 +3223,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3405,7 +3233,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3415,7 +3243,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3425,7 +3253,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3436,14 +3264,14 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:AB2">
-    <cfRule type="duplicateValues" dxfId="27" priority="3"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C4:C31">
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:AB2">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B4816EE8B5370BE58DA68AD559D404E83482B4A7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC16BC0-92CE-4F18-8291-07405153E018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
   <si>
     <t>firstletter</t>
   </si>
@@ -432,6 +432,24 @@
   </si>
   <si>
     <t>door_hard</t>
+  </si>
+  <si>
+    <t>door_extreme</t>
+  </si>
+  <si>
+    <t>Reinforced door</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>prereq</t>
+  </si>
+  <si>
+    <t>Travel to new locations!</t>
+  </si>
+  <si>
+    <t>See available upgrades.</t>
   </si>
 </sst>
 </file>
@@ -1087,9 +1105,15 @@
       <c r="P3" t="s">
         <v>96</v>
       </c>
+      <c r="Q3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="T3" t="str">
-        <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P3),P3,IF(P3="",0,CHAR(39)&amp;P3&amp;CHAR(39)))&amp;"],"</f>
-        <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','coolant','minerals','salvage','description'],</v>
+        <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P3),P3,IF(P3="",0,CHAR(39)&amp;P3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q3),Q3,IF(Q3="",0,CHAR(39)&amp;Q3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R3),R3,IF(R3="",0,CHAR(39)&amp;R3&amp;CHAR(39)))&amp;"],"</f>
+        <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','coolant','minerals','salvage','description','note','prereq'],</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -1123,8 +1147,8 @@
         <v>71</v>
       </c>
       <c r="T4" t="str">
-        <f t="shared" ref="T4:T44" si="1">"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P4),P4,IF(P4="",0,CHAR(39)&amp;P4&amp;CHAR(39)))&amp;"],"</f>
-        <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,0,0],</v>
+        <f t="shared" ref="T4:T38" si="1">"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P4),P4,IF(P4="",0,CHAR(39)&amp;P4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q4),Q4,IF(Q4="",0,CHAR(39)&amp;Q4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R4),R4,IF(R4="",0,CHAR(39)&amp;R4&amp;CHAR(39)))&amp;"],"</f>
+        <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -1160,7 +1184,7 @@
       </c>
       <c r="T5" t="str">
         <f t="shared" si="1"/>
-        <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,0,0],</v>
+        <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,0,0,'upgrade1','reactor'],</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -1196,7 +1220,7 @@
       </c>
       <c r="T6" t="str">
         <f t="shared" si="1"/>
-        <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,0,0],</v>
+        <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -1232,7 +1256,7 @@
       </c>
       <c r="T7" t="str">
         <f t="shared" si="1"/>
-        <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,0,0],</v>
+        <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,0,0,'upgrade1','life'],</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -1268,7 +1292,7 @@
       </c>
       <c r="T8" t="str">
         <f t="shared" si="1"/>
-        <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,0,0],</v>
+        <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,0,0,'upgrade1','life'],</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -1301,7 +1325,7 @@
       </c>
       <c r="T9" t="str">
         <f t="shared" si="1"/>
-        <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,0,0],</v>
+        <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -1337,7 +1361,7 @@
       </c>
       <c r="T10" t="str">
         <f t="shared" si="1"/>
-        <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,0,0],</v>
+        <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,0,0,'upgrade1','cargo'],</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
@@ -1373,7 +1397,7 @@
       </c>
       <c r="T11" t="str">
         <f t="shared" si="1"/>
-        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0],</v>
+        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms'],</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
@@ -1412,7 +1436,7 @@
       </c>
       <c r="T12" t="str">
         <f t="shared" si="1"/>
-        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0],</v>
+        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro'],</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
@@ -1451,7 +1475,7 @@
       </c>
       <c r="T13" t="str">
         <f t="shared" si="1"/>
-        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0],</v>
+        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar'],</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -1485,7 +1509,7 @@
       </c>
       <c r="T14" t="str">
         <f t="shared" si="1"/>
-        <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,0,0,'Allows you to explore space.'],</v>
+        <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,0,0,'Allows you to explore space.','upgrade3','fab,med,anti'],</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
@@ -1509,7 +1533,7 @@
       <c r="Q15" s="8"/>
       <c r="T15" t="str">
         <f t="shared" si="1"/>
-        <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,0,0,'Lets you peek into the endless void of space.'],</v>
+        <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,0,0,'Lets you peek into the endless void of space.',0,0],</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
@@ -1527,14 +1551,16 @@
       <c r="G16" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="P16" s="8"/>
+      <c r="P16" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="Q16" s="8"/>
       <c r="R16" t="s">
         <v>81</v>
       </c>
       <c r="T16" t="str">
         <f t="shared" si="1"/>
-        <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,0],</v>
+        <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,'Travel to new locations!',0,'hazard'],</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -1552,11 +1578,13 @@
       <c r="G17" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="P17" s="8"/>
+      <c r="P17" s="8" t="s">
+        <v>129</v>
+      </c>
       <c r="Q17" s="8"/>
       <c r="T17" t="str">
         <f t="shared" si="1"/>
-        <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,0,0,0],</v>
+        <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,0,0,'See available upgrades.',0,0],</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
@@ -1589,7 +1617,7 @@
       <c r="Q18" s="3"/>
       <c r="T18" t="str">
         <f t="shared" si="1"/>
-        <v>['mining',5,30,'Mining station','CAPTURE',0,0,0,0,0,0,15,0,0],</v>
+        <v>['mining',5,30,'Mining station','CAPTURE',0,0,0,0,0,0,15,0,0,0,0],</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
@@ -1620,7 +1648,7 @@
       <c r="Q19" s="3"/>
       <c r="T19" t="str">
         <f t="shared" si="1"/>
-        <v>['scrapyard',5,30,'Scrapyard','CAPTURE',0,0,0,0,0,0,0,15,0],</v>
+        <v>['scrapyard',5,30,'Scrapyard','CAPTURE',0,0,0,0,0,0,0,15,0,0,0],</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
@@ -1657,7 +1685,7 @@
       <c r="Q20" s="3"/>
       <c r="T20" t="str">
         <f t="shared" si="1"/>
-        <v>['data',5,30,'Data vault','CAPTURE',0,0,0,0,0,5,5,5,0],</v>
+        <v>['data',5,30,'Data vault','CAPTURE',0,0,0,0,0,5,5,5,0,0,0],</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -1685,7 +1713,7 @@
       <c r="Q21" s="3"/>
       <c r="T21" t="str">
         <f t="shared" si="1"/>
-        <v>['supply',5,30,'Supply depot','CAPTURE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['supply',5,30,'Supply depot','CAPTURE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -1716,7 +1744,7 @@
       <c r="Q22" s="3"/>
       <c r="T22" t="str">
         <f t="shared" si="1"/>
-        <v>['fusion',5,40,'Fusion core','CAPTURE',0,0,0,0,15,0,0,0,0],</v>
+        <v>['fusion',5,40,'Fusion core','CAPTURE',0,0,0,0,15,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
@@ -1750,7 +1778,7 @@
       <c r="Q23" s="3"/>
       <c r="T23" t="str">
         <f t="shared" si="1"/>
-        <v>['alloy',5,30,'Alloy plant','CAPTURE',0,0,0,0,0,0,10,5,0],</v>
+        <v>['alloy',5,30,'Alloy plant','CAPTURE',0,0,0,0,0,0,10,5,0,0,0],</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -1787,7 +1815,7 @@
       <c r="Q24" s="3"/>
       <c r="T24" t="str">
         <f t="shared" si="1"/>
-        <v>['research',5,40,'Research lab','CAPTURE',0,0,0,0,5,5,0,5,0],</v>
+        <v>['research',5,40,'Research lab','CAPTURE',0,0,0,0,5,5,0,5,0,0,0],</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
@@ -1813,6 +1841,10 @@
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
+      <c r="T25" t="str">
+        <f t="shared" si="1"/>
+        <v>['chestenergy',0,20,'Energy cells','CLAIM',120,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="14"/>
@@ -1837,6 +1869,10 @@
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
+      <c r="T26" t="str">
+        <f t="shared" si="1"/>
+        <v>['chestwater',0,20,'Ice blocks','CLAIM',0,120,0,0,0,0,0,0,0,0,0],</v>
+      </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
@@ -1861,6 +1897,10 @@
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
+      <c r="T27" t="str">
+        <f t="shared" si="1"/>
+        <v>['chestfood',0,20,'Nutrient packs','CLAIM',0,0,120,0,0,0,0,0,0,0,0],</v>
+      </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
@@ -1885,6 +1925,10 @@
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
+      <c r="T28" t="str">
+        <f t="shared" si="1"/>
+        <v>['chestparts',0,20,'Parts box','CLAIM',0,0,0,120,0,0,0,0,0,0,0],</v>
+      </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
@@ -1911,7 +1955,7 @@
       <c r="Q29" s="3"/>
       <c r="T29" t="str">
         <f t="shared" si="1"/>
-        <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0],</v>
+        <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
@@ -1939,7 +1983,7 @@
       <c r="Q30" s="3"/>
       <c r="T30" t="str">
         <f t="shared" si="1"/>
-        <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0],</v>
+        <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
@@ -1967,7 +2011,7 @@
       <c r="Q31" s="3"/>
       <c r="T31" t="str">
         <f t="shared" si="1"/>
-        <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0],</v>
+        <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0,0,0],</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -1995,7 +2039,7 @@
       <c r="Q32" s="3"/>
       <c r="T32" t="str">
         <f t="shared" si="1"/>
-        <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0],</v>
+        <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0,0,0],</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
@@ -2020,7 +2064,7 @@
       <c r="Q33" s="3"/>
       <c r="T33" t="str">
         <f t="shared" si="1"/>
-        <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0],</v>
+        <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
@@ -2045,7 +2089,7 @@
       <c r="Q34" s="3"/>
       <c r="T34" t="str">
         <f t="shared" si="1"/>
-        <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0],</v>
+        <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
@@ -2061,7 +2105,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="G35" t="s">
         <v>107</v>
@@ -2070,7 +2114,7 @@
       <c r="Q35" s="3"/>
       <c r="T35" t="str">
         <f t="shared" si="1"/>
-        <v>['door_hard',0,50,'High security door','HACK',0,0,0,0,0,0,0,0,0],</v>
+        <v>['door_hard',0,50,'Reinforced door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
@@ -2079,13 +2123,20 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="F36" s="3"/>
+      <c r="C36" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36">
+        <v>70</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="T36" t="str">
         <f t="shared" si="1"/>
-        <v>[0,0,0,0,0,0,0,0,0,0,0,0,0,0],</v>
+        <v>['door_extreme',0,70,'High security door',0,0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.3">
@@ -2112,7 +2163,7 @@
       <c r="Q37" s="9"/>
       <c r="T37" t="str">
         <f t="shared" si="1"/>
-        <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
@@ -2137,7 +2188,7 @@
       <c r="Q38" s="9"/>
       <c r="T38" t="str">
         <f t="shared" si="1"/>
-        <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.3">
@@ -2154,7 +2205,7 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="T39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="T29:T44" si="3">"["&amp;IF(ISNUMBER(C39),C39,IF(C39="",0,CHAR(39)&amp;C39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D39),D39,IF(D39="",0,CHAR(39)&amp;D39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E39),E39,IF(E39="",0,CHAR(39)&amp;E39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F39),F39,IF(F39="",0,CHAR(39)&amp;F39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G39),G39,IF(G39="",0,CHAR(39)&amp;G39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H39),H39,IF(H39="",0,CHAR(39)&amp;H39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I39),I39,IF(I39="",0,CHAR(39)&amp;I39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J39),J39,IF(J39="",0,CHAR(39)&amp;J39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K39),K39,IF(K39="",0,CHAR(39)&amp;K39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L39),L39,IF(L39="",0,CHAR(39)&amp;L39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M39),M39,IF(M39="",0,CHAR(39)&amp;M39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N39),N39,IF(N39="",0,CHAR(39)&amp;N39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O39),O39,IF(O39="",0,CHAR(39)&amp;O39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P39),P39,IF(P39="",0,CHAR(39)&amp;P39&amp;CHAR(39)))&amp;"],"</f>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
@@ -2172,7 +2223,7 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="T40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
@@ -2190,7 +2241,7 @@
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="T41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
@@ -2208,7 +2259,7 @@
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="T42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
@@ -2226,7 +2277,7 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="T43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
@@ -2244,7 +2295,7 @@
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
       <c r="T44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC16BC0-92CE-4F18-8291-07405153E018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A73D56-4FBB-4BDF-8FDD-07529180D6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="131">
   <si>
     <t>firstletter</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>See available upgrades.</t>
+  </si>
+  <si>
+    <t>req hazard on homebase only</t>
   </si>
 </sst>
 </file>
@@ -1554,13 +1557,12 @@
       <c r="P16" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="Q16" s="8"/>
-      <c r="R16" t="s">
-        <v>81</v>
+      <c r="Q16" s="8" t="s">
+        <v>130</v>
       </c>
       <c r="T16" t="str">
         <f t="shared" si="1"/>
-        <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,'Travel to new locations!',0,'hazard'],</v>
+        <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,'Travel to new locations!','req hazard on homebase only',0],</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
@@ -2205,7 +2207,7 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="T39" t="str">
-        <f t="shared" ref="T29:T44" si="3">"["&amp;IF(ISNUMBER(C39),C39,IF(C39="",0,CHAR(39)&amp;C39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D39),D39,IF(D39="",0,CHAR(39)&amp;D39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E39),E39,IF(E39="",0,CHAR(39)&amp;E39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F39),F39,IF(F39="",0,CHAR(39)&amp;F39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G39),G39,IF(G39="",0,CHAR(39)&amp;G39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H39),H39,IF(H39="",0,CHAR(39)&amp;H39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I39),I39,IF(I39="",0,CHAR(39)&amp;I39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J39),J39,IF(J39="",0,CHAR(39)&amp;J39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K39),K39,IF(K39="",0,CHAR(39)&amp;K39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L39),L39,IF(L39="",0,CHAR(39)&amp;L39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M39),M39,IF(M39="",0,CHAR(39)&amp;M39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N39),N39,IF(N39="",0,CHAR(39)&amp;N39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O39),O39,IF(O39="",0,CHAR(39)&amp;O39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P39),P39,IF(P39="",0,CHAR(39)&amp;P39&amp;CHAR(39)))&amp;"],"</f>
+        <f t="shared" ref="T39:T44" si="3">"["&amp;IF(ISNUMBER(C39),C39,IF(C39="",0,CHAR(39)&amp;C39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D39),D39,IF(D39="",0,CHAR(39)&amp;D39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E39),E39,IF(E39="",0,CHAR(39)&amp;E39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F39),F39,IF(F39="",0,CHAR(39)&amp;F39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G39),G39,IF(G39="",0,CHAR(39)&amp;G39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H39),H39,IF(H39="",0,CHAR(39)&amp;H39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I39),I39,IF(I39="",0,CHAR(39)&amp;I39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J39),J39,IF(J39="",0,CHAR(39)&amp;J39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K39),K39,IF(K39="",0,CHAR(39)&amp;K39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L39),L39,IF(L39="",0,CHAR(39)&amp;L39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M39),M39,IF(M39="",0,CHAR(39)&amp;M39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N39),N39,IF(N39="",0,CHAR(39)&amp;N39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O39),O39,IF(O39="",0,CHAR(39)&amp;O39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P39),P39,IF(P39="",0,CHAR(39)&amp;P39&amp;CHAR(39)))&amp;"],"</f>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A73D56-4FBB-4BDF-8FDD-07529180D6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="sheetwithani" sheetId="3" r:id="rId1"/>
     <sheet name="conventions" sheetId="4" r:id="rId2"/>
     <sheet name="bad" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,14 +37,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="139">
   <si>
     <t>firstletter</t>
   </si>
@@ -453,12 +452,36 @@
   </si>
   <si>
     <t>req hazard on homebase only</t>
+  </si>
+  <si>
+    <t>smallenergy</t>
+  </si>
+  <si>
+    <t>smallwater</t>
+  </si>
+  <si>
+    <t>smallfood</t>
+  </si>
+  <si>
+    <t>smallparts</t>
+  </si>
+  <si>
+    <t>Small battery</t>
+  </si>
+  <si>
+    <t>Small water bottle</t>
+  </si>
+  <si>
+    <t>Small candy bar</t>
+  </si>
+  <si>
+    <t>Small circuits</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -980,26 +1003,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T48"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" customWidth="1"/>
+    <col min="1" max="1" width="1.90625" customWidth="1"/>
+    <col min="2" max="2" width="4.08984375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="5.21875" customWidth="1"/>
+    <col min="4" max="4" width="5.1796875" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
-    <col min="8" max="15" width="7.109375" customWidth="1"/>
-    <col min="16" max="16" width="30.77734375" customWidth="1"/>
-    <col min="17" max="17" width="15.21875" customWidth="1"/>
-    <col min="18" max="18" width="12.21875" customWidth="1"/>
-    <col min="19" max="19" width="15.21875" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" customWidth="1"/>
+    <col min="8" max="15" width="7.08984375" customWidth="1"/>
+    <col min="16" max="16" width="30.81640625" customWidth="1"/>
+    <col min="17" max="17" width="15.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.1796875" customWidth="1"/>
+    <col min="19" max="19" width="15.1796875" customWidth="1"/>
+    <col min="20" max="20" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="H1" s="13" t="s">
         <v>60</v>
       </c>
@@ -1022,7 +1045,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>119</v>
       </c>
@@ -1062,7 +1085,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -1119,7 +1142,7 @@
         <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','coolant','minerals','salvage','description','note','prereq'],</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>65</v>
       </c>
@@ -1150,14 +1173,14 @@
         <v>71</v>
       </c>
       <c r="T4" t="str">
-        <f t="shared" ref="T4:T38" si="1">"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P4),P4,IF(P4="",0,CHAR(39)&amp;P4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q4),Q4,IF(Q4="",0,CHAR(39)&amp;Q4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R4),R4,IF(R4="",0,CHAR(39)&amp;R4&amp;CHAR(39)))&amp;"],"</f>
+        <f t="shared" ref="T4:T42" si="1">"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P4),P4,IF(P4="",0,CHAR(39)&amp;P4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q4),Q4,IF(Q4="",0,CHAR(39)&amp;Q4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R4),R4,IF(R4="",0,CHAR(39)&amp;R4&amp;CHAR(39)))&amp;"],"</f>
         <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5">
-        <f t="shared" ref="B5:B44" si="2">SUM(H5:O5)</f>
+        <f t="shared" ref="B5:B48" si="2">SUM(H5:O5)</f>
         <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1190,7 +1213,7 @@
         <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,0,0,'upgrade1','reactor'],</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6">
         <f t="shared" si="2"/>
@@ -1226,7 +1249,7 @@
         <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7">
         <f t="shared" si="2"/>
@@ -1262,7 +1285,7 @@
         <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,0,0,'upgrade1','life'],</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8">
         <f t="shared" si="2"/>
@@ -1298,7 +1321,7 @@
         <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,0,0,'upgrade1','life'],</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9">
         <f t="shared" si="2"/>
@@ -1331,7 +1354,7 @@
         <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10">
         <f t="shared" si="2"/>
@@ -1367,7 +1390,7 @@
         <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,0,0,'upgrade1','cargo'],</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11">
         <f t="shared" si="2"/>
@@ -1403,7 +1426,7 @@
         <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms'],</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12">
         <f t="shared" si="2"/>
@@ -1442,7 +1465,7 @@
         <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro'],</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13">
         <f t="shared" si="2"/>
@@ -1481,7 +1504,7 @@
         <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar'],</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>66</v>
       </c>
@@ -1515,7 +1538,7 @@
         <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,0,0,'Allows you to explore space.','upgrade3','fab,med,anti'],</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="15"/>
       <c r="B15">
         <f t="shared" si="2"/>
@@ -1539,7 +1562,7 @@
         <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,0,0,'Lets you peek into the endless void of space.',0,0],</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="15"/>
       <c r="B16">
         <f t="shared" si="2"/>
@@ -1565,7 +1588,7 @@
         <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,'Travel to new locations!','req hazard on homebase only',0],</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="15"/>
       <c r="B17">
         <f t="shared" si="2"/>
@@ -1589,7 +1612,7 @@
         <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,0,0,'See available upgrades.',0,0],</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="14" t="s">
         <v>67</v>
       </c>
@@ -1622,7 +1645,7 @@
         <v>['mining',5,30,'Mining station','CAPTURE',0,0,0,0,0,0,15,0,0,0,0],</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="14"/>
       <c r="B19">
         <f t="shared" si="2"/>
@@ -1653,7 +1676,7 @@
         <v>['scrapyard',5,30,'Scrapyard','CAPTURE',0,0,0,0,0,0,0,15,0,0,0],</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20">
         <f t="shared" si="2"/>
@@ -1690,7 +1713,7 @@
         <v>['data',5,30,'Data vault','CAPTURE',0,0,0,0,0,5,5,5,0,0,0],</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21">
         <f t="shared" si="2"/>
@@ -1718,7 +1741,7 @@
         <v>['supply',5,30,'Supply depot','CAPTURE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22">
         <f t="shared" si="2"/>
@@ -1749,7 +1772,7 @@
         <v>['fusion',5,40,'Fusion core','CAPTURE',0,0,0,0,15,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23">
         <f t="shared" si="2"/>
@@ -1783,7 +1806,7 @@
         <v>['alloy',5,30,'Alloy plant','CAPTURE',0,0,0,0,0,0,10,5,0,0,0],</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="14"/>
       <c r="B24">
         <f t="shared" si="2"/>
@@ -1820,7 +1843,7 @@
         <v>['research',5,40,'Research lab','CAPTURE',0,0,0,0,5,5,0,5,0,0,0],</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="14"/>
       <c r="B25">
         <f t="shared" si="2"/>
@@ -1848,7 +1871,7 @@
         <v>['chestenergy',0,20,'Energy cells','CLAIM',120,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26">
         <f t="shared" si="2"/>
@@ -1876,7 +1899,7 @@
         <v>['chestwater',0,20,'Ice blocks','CLAIM',0,120,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="14"/>
       <c r="B27">
         <f t="shared" si="2"/>
@@ -1904,7 +1927,7 @@
         <v>['chestfood',0,20,'Nutrient packs','CLAIM',0,0,120,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="14"/>
       <c r="B28">
         <f t="shared" si="2"/>
@@ -1932,340 +1955,380 @@
         <v>['chestparts',0,20,'Parts box','CLAIM',0,0,0,120,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>85</v>
+        <v>131</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s">
         <v>86</v>
       </c>
-      <c r="L29">
-        <v>80</v>
+      <c r="H29">
+        <v>10</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="T29" t="str">
         <f t="shared" si="1"/>
-        <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['smallenergy',0,0,'Small battery','CLAIM',10,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="E30">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="G30" t="s">
         <v>86</v>
       </c>
-      <c r="M30">
-        <v>80</v>
+      <c r="I30">
+        <v>10</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="T30" t="str">
         <f t="shared" si="1"/>
-        <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['smallwater',0,0,'Small water bottle','CLAIM',0,10,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="E31">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
         <v>86</v>
       </c>
-      <c r="N31">
-        <v>80</v>
+      <c r="J31">
+        <v>10</v>
       </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="T31" t="str">
         <f t="shared" si="1"/>
-        <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['smallfood',0,0,'Small candy bar','CLAIM',0,0,10,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="E32">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="G32" t="s">
         <v>86</v>
       </c>
-      <c r="O32">
-        <v>80</v>
+      <c r="K32">
+        <v>10</v>
       </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="T32" t="str">
         <f t="shared" si="1"/>
-        <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0,0,0],</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['smallparts',0,0,'Small circuits','CLAIM',0,0,0,10,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G33" t="s">
-        <v>107</v>
+        <v>86</v>
+      </c>
+      <c r="L33">
+        <v>80</v>
       </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="T33" t="str">
         <f t="shared" si="1"/>
-        <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="14"/>
       <c r="B34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>107</v>
+        <v>86</v>
+      </c>
+      <c r="M34">
+        <v>80</v>
       </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="T34" t="str">
         <f t="shared" si="1"/>
-        <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="14"/>
       <c r="B35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="E35">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s">
-        <v>107</v>
+        <v>86</v>
+      </c>
+      <c r="N35">
+        <v>80</v>
       </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="T35" t="str">
         <f t="shared" si="1"/>
-        <v>['door_hard',0,50,'Reinforced door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="14"/>
       <c r="B36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="E36">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>112</v>
+        <v>89</v>
+      </c>
+      <c r="G36" t="s">
+        <v>86</v>
+      </c>
+      <c r="O36">
+        <v>80</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="T36" t="str">
         <f t="shared" si="1"/>
+        <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0,0,0],</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A37" s="14"/>
+      <c r="B37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G37" t="s">
+        <v>107</v>
+      </c>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="T37" t="str">
+        <f t="shared" si="1"/>
+        <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A38" s="14"/>
+      <c r="B38">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E38">
+        <v>20</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G38" t="s">
+        <v>107</v>
+      </c>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="T38" t="str">
+        <f t="shared" si="1"/>
+        <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A39" s="14"/>
+      <c r="B39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39">
+        <v>50</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G39" t="s">
+        <v>107</v>
+      </c>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="T39" t="str">
+        <f t="shared" si="1"/>
+        <v>['door_hard',0,50,'Reinforced door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A40" s="14"/>
+      <c r="B40">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E40">
+        <v>70</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="T40" t="str">
+        <f t="shared" si="1"/>
         <v>['door_extreme',0,70,'High security door',0,0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A41" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C37" s="9" t="s">
+      <c r="B41">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E37">
-        <v>10</v>
-      </c>
-      <c r="F37" s="9" t="s">
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G37" t="s">
-        <v>108</v>
-      </c>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9"/>
-      <c r="T37" t="str">
-        <f t="shared" si="1"/>
-        <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38">
-        <v>10</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G38" t="s">
-        <v>108</v>
-      </c>
-      <c r="P38" s="9"/>
-      <c r="Q38" s="9"/>
-      <c r="T38" t="str">
-        <f t="shared" si="1"/>
-        <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" t="s">
-        <v>108</v>
-      </c>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9"/>
-      <c r="T39" t="str">
-        <f t="shared" ref="T39:T44" si="3">"["&amp;IF(ISNUMBER(C39),C39,IF(C39="",0,CHAR(39)&amp;C39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D39),D39,IF(D39="",0,CHAR(39)&amp;D39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E39),E39,IF(E39="",0,CHAR(39)&amp;E39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F39),F39,IF(F39="",0,CHAR(39)&amp;F39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G39),G39,IF(G39="",0,CHAR(39)&amp;G39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H39),H39,IF(H39="",0,CHAR(39)&amp;H39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I39),I39,IF(I39="",0,CHAR(39)&amp;I39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J39),J39,IF(J39="",0,CHAR(39)&amp;J39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K39),K39,IF(K39="",0,CHAR(39)&amp;K39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L39),L39,IF(L39="",0,CHAR(39)&amp;L39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M39),M39,IF(M39="",0,CHAR(39)&amp;M39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N39),N39,IF(N39="",0,CHAR(39)&amp;N39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O39),O39,IF(O39="",0,CHAR(39)&amp;O39&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P39),P39,IF(P39="",0,CHAR(39)&amp;P39&amp;CHAR(39)))&amp;"],"</f>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" t="s">
-        <v>108</v>
-      </c>
-      <c r="P40" s="9"/>
-      <c r="Q40" s="9"/>
-      <c r="T40" t="str">
-        <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="F41" s="9"/>
       <c r="G41" t="s">
         <v>108</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="T41" t="str">
-        <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
       <c r="B42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="F42" s="9"/>
+      <c r="C42" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>110</v>
+      </c>
       <c r="G42" t="s">
         <v>108</v>
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="T42" t="str">
-        <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="12"/>
       <c r="B43">
         <f t="shared" si="2"/>
@@ -2279,11 +2342,11 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="T43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="T43:T48" si="3">"["&amp;IF(ISNUMBER(C43),C43,IF(C43="",0,CHAR(39)&amp;C43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D43),D43,IF(D43="",0,CHAR(39)&amp;D43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E43),E43,IF(E43="",0,CHAR(39)&amp;E43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F43),F43,IF(F43="",0,CHAR(39)&amp;F43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G43),G43,IF(G43="",0,CHAR(39)&amp;G43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H43),H43,IF(H43="",0,CHAR(39)&amp;H43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I43),I43,IF(I43="",0,CHAR(39)&amp;I43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J43),J43,IF(J43="",0,CHAR(39)&amp;J43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K43),K43,IF(K43="",0,CHAR(39)&amp;K43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L43),L43,IF(L43="",0,CHAR(39)&amp;L43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M43),M43,IF(M43="",0,CHAR(39)&amp;M43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N43),N43,IF(N43="",0,CHAR(39)&amp;N43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O43),O43,IF(O43="",0,CHAR(39)&amp;O43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P43),P43,IF(P43="",0,CHAR(39)&amp;P43&amp;CHAR(39)))&amp;"],"</f>
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="12"/>
       <c r="B44">
         <f t="shared" si="2"/>
@@ -2301,16 +2364,88 @@
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A45" s="12"/>
+      <c r="B45">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" t="s">
+        <v>108</v>
+      </c>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="T45" t="str">
+        <f t="shared" si="3"/>
+        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A46" s="12"/>
+      <c r="B46">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" t="s">
+        <v>108</v>
+      </c>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="T46" t="str">
+        <f t="shared" si="3"/>
+        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A47" s="12"/>
+      <c r="B47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" t="s">
+        <v>108</v>
+      </c>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="T47" t="str">
+        <f t="shared" si="3"/>
+        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A48" s="12"/>
+      <c r="B48">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" t="s">
+        <v>108</v>
+      </c>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="T48" t="str">
+        <f t="shared" si="3"/>
+        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A37:A44"/>
+    <mergeCell ref="A41:A48"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="A4:A13"/>
-    <mergeCell ref="A18:A36"/>
+    <mergeCell ref="A18:A40"/>
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="A14:A17"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C17 C37:C1048576">
+  <conditionalFormatting sqref="C41:C1048576 C1:C17">
     <cfRule type="duplicateValues" dxfId="11" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
@@ -2319,7 +2454,7 @@
   <conditionalFormatting sqref="D2:O2 T2:U2">
     <cfRule type="duplicateValues" dxfId="9" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E62">
+  <conditionalFormatting sqref="E4:E66">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2331,7 +2466,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37:F44">
+  <conditionalFormatting sqref="F41:F48">
     <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2">
@@ -2340,7 +2475,7 @@
   <conditionalFormatting sqref="P3">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P37:Q44">
+  <conditionalFormatting sqref="P41:Q48">
     <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:R3">
@@ -2355,19 +2490,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="97.44140625" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="97.453125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="97.44140625" style="10"/>
+    <col min="1" max="16384" width="97.453125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>120</v>
       </c>
@@ -2378,17 +2513,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="7.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="5" max="6" width="7.36328125" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -2460,7 +2595,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -2508,7 +2643,7 @@
         <v>["terminal","delay","question","pretty","action","energy","food","water","parts","metals","titanium","alloy"],</v>
       </c>
     </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B4">
         <f>SUM(E4:AA4)</f>
         <v>55</v>
@@ -2540,7 +2675,7 @@
         <v>["reactor",15,0,"Reactor","REPAIR",40,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B5">
         <f t="shared" ref="B5:B31" si="1">SUM(E5:AA5)</f>
         <v>55</v>
@@ -2576,7 +2711,7 @@
         <v xml:space="preserve"> * @property {number} solar</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B6">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -2615,7 +2750,7 @@
         <v xml:space="preserve"> * @property {number} hydro</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B7">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2651,7 +2786,7 @@
         <v xml:space="preserve"> * @property {number} water</v>
       </c>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B8">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2690,7 +2825,7 @@
         <v xml:space="preserve"> * @property {number} cargo</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B9">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -2726,7 +2861,7 @@
         <v xml:space="preserve"> * @property {number} comms</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B10">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -2765,7 +2900,7 @@
         <v xml:space="preserve"> * @property {number} fab</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B11">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2801,7 +2936,7 @@
         <v xml:space="preserve"> * @property {number} med</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B12">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2840,7 +2975,7 @@
         <v xml:space="preserve"> * @property {number} life</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B13">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -2876,7 +3011,7 @@
         <v xml:space="preserve"> * @property {number} machine</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
       <c r="C14" t="str">
         <f t="shared" si="2"/>
         <v>s</v>
@@ -2899,7 +3034,7 @@
         <v xml:space="preserve"> * @property {number} shuttle</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
       <c r="C15" t="str">
         <f t="shared" si="2"/>
         <v>a</v>
@@ -2922,7 +3057,7 @@
         <v xml:space="preserve"> * @property {number} access</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
       <c r="C16" t="str">
         <f t="shared" si="2"/>
         <v>d</v>
@@ -2945,7 +3080,7 @@
         <v xml:space="preserve"> * @property {number} door</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B17">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -2987,7 +3122,7 @@
         <v xml:space="preserve"> * @property {number} mining</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B18">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3026,7 +3161,7 @@
         <v xml:space="preserve"> * @property {number} scrapyard</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B19">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3071,7 +3206,7 @@
         <v xml:space="preserve"> * @property {number} data</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B20">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -3113,7 +3248,7 @@
         <v xml:space="preserve"> * @property {number} supply</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B21">
         <f t="shared" si="1"/>
         <v>140</v>
@@ -3155,7 +3290,7 @@
         <v xml:space="preserve"> * @property {number} fusion</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B22">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -3194,7 +3329,7 @@
         <v xml:space="preserve"> * @property {number} alloy</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B23">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3236,7 +3371,7 @@
         <v xml:space="preserve"> * @property {number} research</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B24">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3246,7 +3381,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3256,7 +3391,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3266,7 +3401,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3276,7 +3411,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3286,7 +3421,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3296,7 +3431,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3306,7 +3441,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="141">
   <si>
     <t>firstletter</t>
   </si>
@@ -298,9 +298,6 @@
     <t>Prerequisite</t>
   </si>
   <si>
-    <t>water,hydro</t>
-  </si>
-  <si>
     <t>fab,med,anti</t>
   </si>
   <si>
@@ -476,6 +473,15 @@
   </si>
   <si>
     <t>Small circuits</t>
+  </si>
+  <si>
+    <t>comms,water,hydro</t>
+  </si>
+  <si>
+    <t>water,hydro,comms,solar</t>
+  </si>
+  <si>
+    <t>solar,comms,water,hydro</t>
   </si>
 </sst>
 </file>
@@ -1036,7 +1042,7 @@
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
       <c r="P1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q1" t="s">
         <v>69</v>
@@ -1047,7 +1053,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H2" s="2" t="str">
         <f>LEFT(H3,1)</f>
@@ -1096,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1129,13 +1135,13 @@
         <v>64</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="T3" t="str">
         <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P3),P3,IF(P3="",0,CHAR(39)&amp;P3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q3),Q3,IF(Q3="",0,CHAR(39)&amp;Q3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R3),R3,IF(R3="",0,CHAR(39)&amp;R3&amp;CHAR(39)))&amp;"],"</f>
@@ -1419,11 +1425,11 @@
         <v>73</v>
       </c>
       <c r="R11" t="s">
-        <v>5</v>
+        <v>138</v>
       </c>
       <c r="T11" t="str">
         <f t="shared" si="1"/>
-        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms'],</v>
+        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms,water,hydro'],</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -1458,11 +1464,11 @@
         <v>73</v>
       </c>
       <c r="R12" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="T12" t="str">
         <f t="shared" si="1"/>
-        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro'],</v>
+        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro,comms,solar'],</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
@@ -1497,11 +1503,11 @@
         <v>73</v>
       </c>
       <c r="R13" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="T13" t="str">
         <f t="shared" si="1"/>
-        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar'],</v>
+        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar,comms,water,hydro'],</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1513,25 +1519,25 @@
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14">
         <v>30</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G14" t="s">
         <v>38</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>74</v>
       </c>
       <c r="R14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T14" t="str">
         <f t="shared" si="1"/>
@@ -1554,7 +1560,7 @@
         <v>77</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="T15" t="str">
@@ -1575,13 +1581,13 @@
         <v>29</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T16" t="str">
         <f t="shared" si="1"/>
@@ -1595,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q17" s="8"/>
       <c r="T17" t="str">
@@ -1850,16 +1856,16 @@
         <v>120</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25">
         <v>120</v>
@@ -1878,16 +1884,16 @@
         <v>120</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26">
         <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26">
         <v>120</v>
@@ -1906,16 +1912,16 @@
         <v>120</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J27">
         <v>120</v>
@@ -1934,16 +1940,16 @@
         <v>120</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E28">
         <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K28">
         <v>120</v>
@@ -1962,16 +1968,16 @@
         <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H29">
         <v>10</v>
@@ -1990,16 +1996,16 @@
         <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I30">
         <v>10</v>
@@ -2018,16 +2024,16 @@
         <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J31">
         <v>10</v>
@@ -2046,16 +2052,16 @@
         <v>10</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K32">
         <v>10</v>
@@ -2074,16 +2080,16 @@
         <v>80</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E33">
         <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L33">
         <v>80</v>
@@ -2102,16 +2108,16 @@
         <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E34">
         <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M34">
         <v>80</v>
@@ -2130,16 +2136,16 @@
         <v>80</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E35">
         <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N35">
         <v>80</v>
@@ -2158,16 +2164,16 @@
         <v>80</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36">
         <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O36">
         <v>80</v>
@@ -2186,16 +2192,16 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
@@ -2211,16 +2217,16 @@
         <v>0</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E38">
         <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
@@ -2236,16 +2242,16 @@
         <v>0</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E39">
         <v>50</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
@@ -2261,13 +2267,13 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E40">
         <v>70</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
@@ -2278,23 +2284,23 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C41" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="G41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
@@ -2310,16 +2316,16 @@
         <v>0</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E42">
-        <v>10</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="G42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
@@ -2337,7 +2343,7 @@
       <c r="C43" s="9"/>
       <c r="F43" s="9"/>
       <c r="G43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
@@ -2355,7 +2361,7 @@
       <c r="C44" s="9"/>
       <c r="F44" s="9"/>
       <c r="G44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
@@ -2373,7 +2379,7 @@
       <c r="C45" s="9"/>
       <c r="F45" s="9"/>
       <c r="G45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
@@ -2391,7 +2397,7 @@
       <c r="C46" s="9"/>
       <c r="F46" s="9"/>
       <c r="G46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
@@ -2409,7 +2415,7 @@
       <c r="C47" s="9"/>
       <c r="F47" s="9"/>
       <c r="G47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
@@ -2427,7 +2433,7 @@
       <c r="C48" s="9"/>
       <c r="F48" s="9"/>
       <c r="G48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
@@ -2499,12 +2505,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="139">
   <si>
     <t>firstletter</t>
   </si>
@@ -475,13 +475,7 @@
     <t>Small circuits</t>
   </si>
   <si>
-    <t>comms,water,hydro</t>
-  </si>
-  <si>
     <t>water,hydro,comms,solar</t>
-  </si>
-  <si>
-    <t>solar,comms,water,hydro</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1423,7 @@
       </c>
       <c r="T11" t="str">
         <f t="shared" si="1"/>
-        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms,water,hydro'],</v>
+        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','water,hydro,comms,solar'],</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -1464,7 +1458,7 @@
         <v>73</v>
       </c>
       <c r="R12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T12" t="str">
         <f t="shared" si="1"/>
@@ -1503,11 +1497,11 @@
         <v>73</v>
       </c>
       <c r="R13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="T13" t="str">
         <f t="shared" si="1"/>
-        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar,comms,water,hydro'],</v>
+        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','water,hydro,comms,solar'],</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="147">
   <si>
     <t>firstletter</t>
   </si>
@@ -476,6 +476,30 @@
   </si>
   <si>
     <t>water,hydro,comms,solar</t>
+  </si>
+  <si>
+    <t>sink</t>
+  </si>
+  <si>
+    <t>Sink</t>
+  </si>
+  <si>
+    <t>shower</t>
+  </si>
+  <si>
+    <t>Shower</t>
+  </si>
+  <si>
+    <t>sofa</t>
+  </si>
+  <si>
+    <t>Sofa</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>Table</t>
   </si>
 </sst>
 </file>
@@ -1419,11 +1443,11 @@
         <v>73</v>
       </c>
       <c r="R11" t="s">
-        <v>138</v>
+        <v>5</v>
       </c>
       <c r="T11" t="str">
         <f t="shared" si="1"/>
-        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','water,hydro,comms,solar'],</v>
+        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms'],</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
@@ -1497,11 +1521,11 @@
         <v>73</v>
       </c>
       <c r="R13" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="T13" t="str">
         <f t="shared" si="1"/>
-        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','water,hydro,comms,solar'],</v>
+        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar'],</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2334,8 +2358,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="F43" s="9"/>
+      <c r="C43" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>140</v>
+      </c>
       <c r="G43" t="s">
         <v>107</v>
       </c>
@@ -2343,7 +2374,7 @@
       <c r="Q43" s="9"/>
       <c r="T43" t="str">
         <f t="shared" ref="T43:T48" si="3">"["&amp;IF(ISNUMBER(C43),C43,IF(C43="",0,CHAR(39)&amp;C43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D43),D43,IF(D43="",0,CHAR(39)&amp;D43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E43),E43,IF(E43="",0,CHAR(39)&amp;E43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F43),F43,IF(F43="",0,CHAR(39)&amp;F43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G43),G43,IF(G43="",0,CHAR(39)&amp;G43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H43),H43,IF(H43="",0,CHAR(39)&amp;H43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I43),I43,IF(I43="",0,CHAR(39)&amp;I43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J43),J43,IF(J43="",0,CHAR(39)&amp;J43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K43),K43,IF(K43="",0,CHAR(39)&amp;K43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L43),L43,IF(L43="",0,CHAR(39)&amp;L43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M43),M43,IF(M43="",0,CHAR(39)&amp;M43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N43),N43,IF(N43="",0,CHAR(39)&amp;N43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O43),O43,IF(O43="",0,CHAR(39)&amp;O43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P43),P43,IF(P43="",0,CHAR(39)&amp;P43&amp;CHAR(39)))&amp;"],"</f>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['sink',0,10,'Sink','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.35">
@@ -2352,8 +2383,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="F44" s="9"/>
+      <c r="C44" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="G44" t="s">
         <v>107</v>
       </c>
@@ -2361,7 +2399,7 @@
       <c r="Q44" s="9"/>
       <c r="T44" t="str">
         <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['shower',0,10,'Shower','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
@@ -2370,8 +2408,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="F45" s="9"/>
+      <c r="C45" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="G45" t="s">
         <v>107</v>
       </c>
@@ -2379,7 +2424,7 @@
       <c r="Q45" s="9"/>
       <c r="T45" t="str">
         <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['sofa',0,10,'Sofa','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.35">
@@ -2388,8 +2433,15 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="F46" s="9"/>
+      <c r="C46" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>146</v>
+      </c>
       <c r="G46" t="s">
         <v>107</v>
       </c>
@@ -2397,7 +2449,7 @@
       <c r="Q46" s="9"/>
       <c r="T46" t="str">
         <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+        <v>['table',0,10,'Table','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.35">

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51992DB-79B3-40DC-9BCB-1782D7A37E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheetwithani" sheetId="3" r:id="rId1"/>
     <sheet name="conventions" sheetId="4" r:id="rId2"/>
     <sheet name="bad" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -475,9 +476,6 @@
     <t>Small circuits</t>
   </si>
   <si>
-    <t>water,hydro,comms,solar</t>
-  </si>
-  <si>
     <t>sink</t>
   </si>
   <si>
@@ -500,12 +498,15 @@
   </si>
   <si>
     <t>Table</t>
+  </si>
+  <si>
+    <t>water,hydro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -733,6 +734,7 @@
       <font>
         <b/>
         <i val="0"/>
+        <strike/>
       </font>
       <fill>
         <patternFill>
@@ -744,7 +746,6 @@
       <font>
         <b/>
         <i val="0"/>
-        <strike/>
       </font>
       <fill>
         <patternFill>
@@ -1027,26 +1028,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" customWidth="1"/>
-    <col min="2" max="2" width="4.08984375" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="20.36328125" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" customWidth="1"/>
-    <col min="8" max="15" width="7.08984375" customWidth="1"/>
-    <col min="16" max="16" width="30.81640625" customWidth="1"/>
-    <col min="17" max="17" width="15.1796875" customWidth="1"/>
-    <col min="18" max="18" width="12.1796875" customWidth="1"/>
-    <col min="19" max="19" width="15.1796875" customWidth="1"/>
-    <col min="20" max="20" width="15.36328125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="15" width="7.109375" customWidth="1"/>
+    <col min="16" max="16" width="30.77734375" customWidth="1"/>
+    <col min="17" max="17" width="15.21875" customWidth="1"/>
+    <col min="18" max="18" width="12.21875" customWidth="1"/>
+    <col min="19" max="19" width="15.21875" customWidth="1"/>
+    <col min="20" max="20" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="H1" s="13" t="s">
         <v>60</v>
       </c>
@@ -1069,7 +1070,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>118</v>
       </c>
@@ -1109,7 +1110,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -1166,7 +1167,7 @@
         <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','coolant','minerals','salvage','description','note','prereq'],</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>65</v>
       </c>
@@ -1201,7 +1202,7 @@
         <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5">
         <f t="shared" ref="B5:B48" si="2">SUM(H5:O5)</f>
@@ -1237,7 +1238,7 @@
         <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,0,0,'upgrade1','reactor'],</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6">
         <f t="shared" si="2"/>
@@ -1273,7 +1274,7 @@
         <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7">
         <f t="shared" si="2"/>
@@ -1309,7 +1310,7 @@
         <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,0,0,'upgrade1','life'],</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="12"/>
       <c r="B8">
         <f t="shared" si="2"/>
@@ -1345,7 +1346,7 @@
         <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,0,0,'upgrade1','life'],</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9">
         <f t="shared" si="2"/>
@@ -1378,7 +1379,7 @@
         <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,0,0,'base',0],</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10">
         <f t="shared" si="2"/>
@@ -1414,7 +1415,7 @@
         <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,0,0,'upgrade1','cargo'],</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="12"/>
       <c r="B11">
         <f t="shared" si="2"/>
@@ -1450,7 +1451,7 @@
         <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms'],</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="12"/>
       <c r="B12">
         <f t="shared" si="2"/>
@@ -1482,14 +1483,14 @@
         <v>73</v>
       </c>
       <c r="R12" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="T12" t="str">
         <f t="shared" si="1"/>
-        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro,comms,solar'],</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro'],</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="12"/>
       <c r="B13">
         <f t="shared" si="2"/>
@@ -1528,7 +1529,7 @@
         <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar'],</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>66</v>
       </c>
@@ -1562,7 +1563,7 @@
         <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,0,0,'Allows you to explore space.','upgrade3','fab,med,anti'],</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15">
         <f t="shared" si="2"/>
@@ -1586,7 +1587,7 @@
         <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,0,0,'Lets you peek into the endless void of space.',0,0],</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16">
         <f t="shared" si="2"/>
@@ -1612,7 +1613,7 @@
         <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,'Travel to new locations!','req hazard on homebase only',0],</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="15"/>
       <c r="B17">
         <f t="shared" si="2"/>
@@ -1636,7 +1637,7 @@
         <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,0,0,'See available upgrades.',0,0],</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>67</v>
       </c>
@@ -1669,7 +1670,7 @@
         <v>['mining',5,30,'Mining station','CAPTURE',0,0,0,0,0,0,15,0,0,0,0],</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="14"/>
       <c r="B19">
         <f t="shared" si="2"/>
@@ -1700,7 +1701,7 @@
         <v>['scrapyard',5,30,'Scrapyard','CAPTURE',0,0,0,0,0,0,0,15,0,0,0],</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="14"/>
       <c r="B20">
         <f t="shared" si="2"/>
@@ -1737,7 +1738,7 @@
         <v>['data',5,30,'Data vault','CAPTURE',0,0,0,0,0,5,5,5,0,0,0],</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="14"/>
       <c r="B21">
         <f t="shared" si="2"/>
@@ -1765,7 +1766,7 @@
         <v>['supply',5,30,'Supply depot','CAPTURE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
       <c r="B22">
         <f t="shared" si="2"/>
@@ -1796,7 +1797,7 @@
         <v>['fusion',5,40,'Fusion core','CAPTURE',0,0,0,0,15,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="14"/>
       <c r="B23">
         <f t="shared" si="2"/>
@@ -1830,7 +1831,7 @@
         <v>['alloy',5,30,'Alloy plant','CAPTURE',0,0,0,0,0,0,10,5,0,0,0],</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="14"/>
       <c r="B24">
         <f t="shared" si="2"/>
@@ -1867,7 +1868,7 @@
         <v>['research',5,40,'Research lab','CAPTURE',0,0,0,0,5,5,0,5,0,0,0],</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="14"/>
       <c r="B25">
         <f t="shared" si="2"/>
@@ -1895,7 +1896,7 @@
         <v>['chestenergy',0,20,'Energy cells','CLAIM',120,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="14"/>
       <c r="B26">
         <f t="shared" si="2"/>
@@ -1923,7 +1924,7 @@
         <v>['chestwater',0,20,'Ice blocks','CLAIM',0,120,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
       <c r="B27">
         <f t="shared" si="2"/>
@@ -1951,7 +1952,7 @@
         <v>['chestfood',0,20,'Nutrient packs','CLAIM',0,0,120,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
       <c r="B28">
         <f t="shared" si="2"/>
@@ -1979,7 +1980,7 @@
         <v>['chestparts',0,20,'Parts box','CLAIM',0,0,0,120,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29">
         <f t="shared" si="2"/>
@@ -2007,7 +2008,7 @@
         <v>['smallenergy',0,0,'Small battery','CLAIM',10,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="14"/>
       <c r="B30">
         <f t="shared" si="2"/>
@@ -2035,7 +2036,7 @@
         <v>['smallwater',0,0,'Small water bottle','CLAIM',0,10,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
       <c r="B31">
         <f t="shared" si="2"/>
@@ -2063,7 +2064,7 @@
         <v>['smallfood',0,0,'Small candy bar','CLAIM',0,0,10,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32">
         <f t="shared" si="2"/>
@@ -2091,7 +2092,7 @@
         <v>['smallparts',0,0,'Small circuits','CLAIM',0,0,0,10,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
       <c r="B33">
         <f t="shared" si="2"/>
@@ -2119,7 +2120,7 @@
         <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
       <c r="B34">
         <f t="shared" si="2"/>
@@ -2147,7 +2148,7 @@
         <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
       <c r="B35">
         <f t="shared" si="2"/>
@@ -2175,7 +2176,7 @@
         <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0,0,0],</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="14"/>
       <c r="B36">
         <f t="shared" si="2"/>
@@ -2203,7 +2204,7 @@
         <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0,0,0],</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="14"/>
       <c r="B37">
         <f t="shared" si="2"/>
@@ -2228,7 +2229,7 @@
         <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="14"/>
       <c r="B38">
         <f t="shared" si="2"/>
@@ -2253,7 +2254,7 @@
         <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="14"/>
       <c r="B39">
         <f t="shared" si="2"/>
@@ -2278,7 +2279,7 @@
         <v>['door_hard',0,50,'Reinforced door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="14"/>
       <c r="B40">
         <f t="shared" si="2"/>
@@ -2300,7 +2301,7 @@
         <v>['door_extreme',0,70,'High security door',0,0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>94</v>
       </c>
@@ -2327,7 +2328,7 @@
         <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="12"/>
       <c r="B42">
         <f t="shared" si="2"/>
@@ -2352,20 +2353,20 @@
         <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="12"/>
       <c r="B43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C43" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="E43">
-        <v>10</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>140</v>
       </c>
       <c r="G43" t="s">
         <v>107</v>
@@ -2377,20 +2378,20 @@
         <v>['sink',0,10,'Sink','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="12"/>
       <c r="B44">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="E44">
-        <v>10</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="G44" t="s">
         <v>107</v>
@@ -2402,20 +2403,20 @@
         <v>['shower',0,10,'Shower','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C45" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="E45">
-        <v>10</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>144</v>
       </c>
       <c r="G45" t="s">
         <v>107</v>
@@ -2427,20 +2428,20 @@
         <v>['sofa',0,10,'Sofa','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="12"/>
       <c r="B46">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="E46">
-        <v>10</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="G46" t="s">
         <v>107</v>
@@ -2452,7 +2453,7 @@
         <v>['table',0,10,'Table','RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="12"/>
       <c r="B47">
         <f t="shared" si="2"/>
@@ -2470,7 +2471,7 @@
         <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="12"/>
       <c r="B48">
         <f t="shared" si="2"/>
@@ -2497,11 +2498,11 @@
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="A14:A17"/>
   </mergeCells>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C41:C1048576 C1:C17">
-    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:O2 T2:U2">
     <cfRule type="duplicateValues" dxfId="9" priority="15"/>
@@ -2542,19 +2543,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="97.453125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="97.44140625" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="97.453125" style="10"/>
+    <col min="1" max="16384" width="97.44140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>119</v>
       </c>
@@ -2565,17 +2566,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:Z31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="7.36328125" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" customWidth="1"/>
+    <col min="5" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -2647,7 +2648,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -2695,7 +2696,7 @@
         <v>["terminal","delay","question","pretty","action","energy","food","water","parts","metals","titanium","alloy"],</v>
       </c>
     </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B4">
         <f>SUM(E4:AA4)</f>
         <v>55</v>
@@ -2727,7 +2728,7 @@
         <v>["reactor",15,0,"Reactor","REPAIR",40,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B5">
         <f t="shared" ref="B5:B31" si="1">SUM(E5:AA5)</f>
         <v>55</v>
@@ -2763,7 +2764,7 @@
         <v xml:space="preserve"> * @property {number} solar</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B6">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -2802,7 +2803,7 @@
         <v xml:space="preserve"> * @property {number} hydro</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2838,7 +2839,7 @@
         <v xml:space="preserve"> * @property {number} water</v>
       </c>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2877,7 +2878,7 @@
         <v xml:space="preserve"> * @property {number} cargo</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B9">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -2913,7 +2914,7 @@
         <v xml:space="preserve"> * @property {number} comms</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B10">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -2952,7 +2953,7 @@
         <v xml:space="preserve"> * @property {number} fab</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B11">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2988,7 +2989,7 @@
         <v xml:space="preserve"> * @property {number} med</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B12">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3027,7 +3028,7 @@
         <v xml:space="preserve"> * @property {number} life</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B13">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -3063,7 +3064,7 @@
         <v xml:space="preserve"> * @property {number} machine</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C14" t="str">
         <f t="shared" si="2"/>
         <v>s</v>
@@ -3086,7 +3087,7 @@
         <v xml:space="preserve"> * @property {number} shuttle</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f t="shared" si="2"/>
         <v>a</v>
@@ -3109,7 +3110,7 @@
         <v xml:space="preserve"> * @property {number} access</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f t="shared" si="2"/>
         <v>d</v>
@@ -3132,7 +3133,7 @@
         <v xml:space="preserve"> * @property {number} door</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3174,7 +3175,7 @@
         <v xml:space="preserve"> * @property {number} mining</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3213,7 +3214,7 @@
         <v xml:space="preserve"> * @property {number} scrapyard</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3258,7 +3259,7 @@
         <v xml:space="preserve"> * @property {number} data</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -3300,7 +3301,7 @@
         <v xml:space="preserve"> * @property {number} supply</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21">
         <f t="shared" si="1"/>
         <v>140</v>
@@ -3342,7 +3343,7 @@
         <v xml:space="preserve"> * @property {number} fusion</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -3381,7 +3382,7 @@
         <v xml:space="preserve"> * @property {number} alloy</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3423,7 +3424,7 @@
         <v xml:space="preserve"> * @property {number} research</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3433,7 +3434,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3443,7 +3444,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3453,7 +3454,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3463,7 +3464,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3473,7 +3474,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3483,7 +3484,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3493,7 +3494,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51992DB-79B3-40DC-9BCB-1782D7A37E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="sheetwithani" sheetId="3" r:id="rId1"/>
     <sheet name="conventions" sheetId="4" r:id="rId2"/>
     <sheet name="bad" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,14 +37,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="137">
   <si>
     <t>firstletter</t>
   </si>
@@ -248,24 +247,12 @@
     <t>antimatter</t>
   </si>
   <si>
-    <t>coolant</t>
-  </si>
-  <si>
-    <t>minerals</t>
-  </si>
-  <si>
-    <t>salvage</t>
-  </si>
-  <si>
     <t>homebase</t>
   </si>
   <si>
     <t>utility</t>
   </si>
   <si>
-    <t>hostile</t>
-  </si>
-  <si>
     <t>Hostile</t>
   </si>
   <si>
@@ -305,30 +292,9 @@
     <t>hazard</t>
   </si>
   <si>
-    <t>chestmineral</t>
-  </si>
-  <si>
-    <t>chestcoolant</t>
-  </si>
-  <si>
-    <t>chestsalvage</t>
-  </si>
-  <si>
-    <t>chestantimatter</t>
-  </si>
-  <si>
     <t>CLAIM</t>
   </si>
   <si>
-    <t>Mineral residue</t>
-  </si>
-  <si>
-    <t>Coolant remains</t>
-  </si>
-  <si>
-    <t>Salvage pack</t>
-  </si>
-  <si>
     <t>Antimatter traces</t>
   </si>
   <si>
@@ -501,12 +467,15 @@
   </si>
   <si>
     <t>water,hydro</t>
+  </si>
+  <si>
+    <t>chestanti</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -590,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -606,6 +575,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -1028,58 +1000,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" customWidth="1"/>
+    <col min="1" max="1" width="1.90625" customWidth="1"/>
+    <col min="2" max="2" width="4.08984375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="5.21875" customWidth="1"/>
+    <col min="4" max="4" width="5.1796875" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
-    <col min="8" max="15" width="7.109375" customWidth="1"/>
-    <col min="16" max="16" width="30.77734375" customWidth="1"/>
-    <col min="17" max="17" width="15.21875" customWidth="1"/>
-    <col min="18" max="18" width="12.21875" customWidth="1"/>
-    <col min="19" max="19" width="15.21875" customWidth="1"/>
-    <col min="20" max="20" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.36328125" customWidth="1"/>
+    <col min="7" max="7" width="12.81640625" customWidth="1"/>
+    <col min="8" max="12" width="7.08984375" customWidth="1"/>
+    <col min="13" max="13" width="30.81640625" customWidth="1"/>
+    <col min="14" max="14" width="15.1796875" customWidth="1"/>
+    <col min="15" max="15" width="12.1796875" customWidth="1"/>
+    <col min="16" max="16" width="15.1796875" customWidth="1"/>
+    <col min="17" max="17" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="H1" s="13" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="H1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>69</v>
-      </c>
-      <c r="R1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H2" s="2" t="str">
         <f>LEFT(H3,1)</f>
         <v>e</v>
       </c>
       <c r="I2" s="2" t="str">
-        <f t="shared" ref="I2:O2" si="0">LEFT(I3,1)</f>
+        <f t="shared" ref="I2:L2" si="0">LEFT(I3,1)</f>
         <v>w</v>
       </c>
       <c r="J2" s="2" t="str">
@@ -1094,23 +1063,11 @@
         <f t="shared" si="0"/>
         <v>a</v>
       </c>
-      <c r="M2" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>c</v>
-      </c>
-      <c r="N2" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>m</v>
-      </c>
-      <c r="O2" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>s</v>
-      </c>
-      <c r="S2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="P2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -1121,7 +1078,7 @@
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -1144,35 +1101,26 @@
       <c r="L3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q3" t="e">
+        <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="P3" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="T3" t="str">
-        <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P3),P3,IF(P3="",0,CHAR(39)&amp;P3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q3),Q3,IF(Q3="",0,CHAR(39)&amp;Q3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R3),R3,IF(R3="",0,CHAR(39)&amp;R3&amp;CHAR(39)))&amp;"],"</f>
-        <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','coolant','minerals','salvage','description','note','prereq'],</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="B4">
-        <f>SUM(H4:O4)</f>
+        <f>SUM(H4:L4)</f>
         <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1193,19 +1141,19 @@
       <c r="H4">
         <v>50</v>
       </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="T4" t="str">
-        <f t="shared" ref="T4:T42" si="1">"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P4),P4,IF(P4="",0,CHAR(39)&amp;P4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(Q4),Q4,IF(Q4="",0,CHAR(39)&amp;Q4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(R4),R4,IF(R4="",0,CHAR(39)&amp;R4&amp;CHAR(39)))&amp;"],"</f>
-        <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,0,0,'base',0],</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" t="e">
+        <f>"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="13"/>
       <c r="B5">
-        <f t="shared" ref="B5:B48" si="2">SUM(H5:O5)</f>
+        <f>SUM(H5:L5)</f>
         <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1226,22 +1174,22 @@
       <c r="H5">
         <v>30</v>
       </c>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" t="s">
         <v>1</v>
       </c>
-      <c r="T5" t="str">
-        <f t="shared" si="1"/>
-        <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,0,0,'upgrade1','reactor'],</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
+      <c r="Q5" t="e">
+        <f>"["&amp;IF(ISNUMBER(C5),C5,IF(C5="",0,CHAR(39)&amp;C5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D5),D5,IF(D5="",0,CHAR(39)&amp;D5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E5),E5,IF(E5="",0,CHAR(39)&amp;E5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F5),F5,IF(F5="",0,CHAR(39)&amp;F5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G5),G5,IF(G5="",0,CHAR(39)&amp;G5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H5),H5,IF(H5="",0,CHAR(39)&amp;H5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I5),I5,IF(I5="",0,CHAR(39)&amp;I5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J5),J5,IF(J5="",0,CHAR(39)&amp;J5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K5),K5,IF(K5="",0,CHAR(39)&amp;K5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L5),L5,IF(L5="",0,CHAR(39)&amp;L5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M5),M5,IF(M5="",0,CHAR(39)&amp;M5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N5),N5,IF(N5="",0,CHAR(39)&amp;N5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O5),O5,IF(O5="",0,CHAR(39)&amp;O5&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="13"/>
       <c r="B6">
-        <f t="shared" si="2"/>
+        <f>SUM(H6:L6)</f>
         <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1265,19 +1213,19 @@
       <c r="J6">
         <v>20</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="T6" t="str">
-        <f t="shared" si="1"/>
-        <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,0,0,'base',0],</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q6" t="e">
+        <f>"["&amp;IF(ISNUMBER(C6),C6,IF(C6="",0,CHAR(39)&amp;C6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D6),D6,IF(D6="",0,CHAR(39)&amp;D6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E6),E6,IF(E6="",0,CHAR(39)&amp;E6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F6),F6,IF(F6="",0,CHAR(39)&amp;F6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G6),G6,IF(G6="",0,CHAR(39)&amp;G6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H6),H6,IF(H6="",0,CHAR(39)&amp;H6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I6),I6,IF(I6="",0,CHAR(39)&amp;I6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J6),J6,IF(J6="",0,CHAR(39)&amp;J6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K6),K6,IF(K6="",0,CHAR(39)&amp;K6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L6),L6,IF(L6="",0,CHAR(39)&amp;L6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M6),M6,IF(M6="",0,CHAR(39)&amp;M6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N6),N6,IF(N6="",0,CHAR(39)&amp;N6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O6),O6,IF(O6="",0,CHAR(39)&amp;O6&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="13"/>
       <c r="B7">
-        <f t="shared" si="2"/>
+        <f>SUM(H7:L7)</f>
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1298,22 +1246,22 @@
       <c r="I7">
         <v>30</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="R7" t="s">
+      <c r="M7" s="5"/>
+      <c r="N7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" t="s">
         <v>44</v>
       </c>
-      <c r="T7" t="str">
-        <f t="shared" si="1"/>
-        <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,0,0,'upgrade1','life'],</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
+      <c r="Q7" t="e">
+        <f>"["&amp;IF(ISNUMBER(C7),C7,IF(C7="",0,CHAR(39)&amp;C7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D7),D7,IF(D7="",0,CHAR(39)&amp;D7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E7),E7,IF(E7="",0,CHAR(39)&amp;E7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F7),F7,IF(F7="",0,CHAR(39)&amp;F7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G7),G7,IF(G7="",0,CHAR(39)&amp;G7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H7),H7,IF(H7="",0,CHAR(39)&amp;H7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I7),I7,IF(I7="",0,CHAR(39)&amp;I7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J7),J7,IF(J7="",0,CHAR(39)&amp;J7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K7),K7,IF(K7="",0,CHAR(39)&amp;K7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L7),L7,IF(L7="",0,CHAR(39)&amp;L7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M7),M7,IF(M7="",0,CHAR(39)&amp;M7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N7),N7,IF(N7="",0,CHAR(39)&amp;N7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O7),O7,IF(O7="",0,CHAR(39)&amp;O7&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="13"/>
       <c r="B8">
-        <f t="shared" si="2"/>
+        <f>SUM(H8:L8)</f>
         <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1334,22 +1282,22 @@
       <c r="J8">
         <v>30</v>
       </c>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" t="s">
         <v>44</v>
       </c>
-      <c r="T8" t="str">
-        <f t="shared" si="1"/>
-        <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,0,0,'upgrade1','life'],</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
+      <c r="Q8" t="e">
+        <f>"["&amp;IF(ISNUMBER(C8),C8,IF(C8="",0,CHAR(39)&amp;C8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D8),D8,IF(D8="",0,CHAR(39)&amp;D8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E8),E8,IF(E8="",0,CHAR(39)&amp;E8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F8),F8,IF(F8="",0,CHAR(39)&amp;F8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G8),G8,IF(G8="",0,CHAR(39)&amp;G8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H8),H8,IF(H8="",0,CHAR(39)&amp;H8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I8),I8,IF(I8="",0,CHAR(39)&amp;I8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J8),J8,IF(J8="",0,CHAR(39)&amp;J8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K8),K8,IF(K8="",0,CHAR(39)&amp;K8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L8),L8,IF(L8="",0,CHAR(39)&amp;L8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M8),M8,IF(M8="",0,CHAR(39)&amp;M8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N8),N8,IF(N8="",0,CHAR(39)&amp;N8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O8),O8,IF(O8="",0,CHAR(39)&amp;O8&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="13"/>
       <c r="B9">
-        <f t="shared" si="2"/>
+        <f>SUM(H9:L9)</f>
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1370,19 +1318,19 @@
       <c r="K9">
         <v>20</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="T9" t="str">
-        <f t="shared" si="1"/>
-        <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,0,0,'base',0],</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q9" t="e">
+        <f>"["&amp;IF(ISNUMBER(C9),C9,IF(C9="",0,CHAR(39)&amp;C9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D9),D9,IF(D9="",0,CHAR(39)&amp;D9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E9),E9,IF(E9="",0,CHAR(39)&amp;E9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F9),F9,IF(F9="",0,CHAR(39)&amp;F9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G9),G9,IF(G9="",0,CHAR(39)&amp;G9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H9),H9,IF(H9="",0,CHAR(39)&amp;H9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I9),I9,IF(I9="",0,CHAR(39)&amp;I9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J9),J9,IF(J9="",0,CHAR(39)&amp;J9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K9),K9,IF(K9="",0,CHAR(39)&amp;K9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L9),L9,IF(L9="",0,CHAR(39)&amp;L9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M9),M9,IF(M9="",0,CHAR(39)&amp;M9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N9),N9,IF(N9="",0,CHAR(39)&amp;N9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O9),O9,IF(O9="",0,CHAR(39)&amp;O9&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="13"/>
       <c r="B10">
-        <f t="shared" si="2"/>
+        <f>SUM(H10:L10)</f>
         <v>50</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1403,22 +1351,22 @@
       <c r="K10">
         <v>50</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="R10" t="s">
+      <c r="M10" s="5"/>
+      <c r="N10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" t="s">
         <v>42</v>
       </c>
-      <c r="T10" t="str">
-        <f t="shared" si="1"/>
-        <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,0,0,'upgrade1','cargo'],</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
+      <c r="Q10" t="e">
+        <f>"["&amp;IF(ISNUMBER(C10),C10,IF(C10="",0,CHAR(39)&amp;C10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D10),D10,IF(D10="",0,CHAR(39)&amp;D10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E10),E10,IF(E10="",0,CHAR(39)&amp;E10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F10),F10,IF(F10="",0,CHAR(39)&amp;F10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G10),G10,IF(G10="",0,CHAR(39)&amp;G10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H10),H10,IF(H10="",0,CHAR(39)&amp;H10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I10),I10,IF(I10="",0,CHAR(39)&amp;I10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J10),J10,IF(J10="",0,CHAR(39)&amp;J10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K10),K10,IF(K10="",0,CHAR(39)&amp;K10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L10),L10,IF(L10="",0,CHAR(39)&amp;L10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M10),M10,IF(M10="",0,CHAR(39)&amp;M10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N10),N10,IF(N10="",0,CHAR(39)&amp;N10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O10),O10,IF(O10="",0,CHAR(39)&amp;O10&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="13"/>
       <c r="B11">
-        <f t="shared" si="2"/>
+        <f>SUM(H11:L11)</f>
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1439,22 +1387,22 @@
       <c r="K11">
         <v>10</v>
       </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="M11" s="6"/>
+      <c r="N11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11" t="s">
         <v>5</v>
       </c>
-      <c r="T11" t="str">
-        <f t="shared" si="1"/>
-        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,0,0,'upgrade2','comms'],</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
+      <c r="Q11" t="e">
+        <f>"["&amp;IF(ISNUMBER(C11),C11,IF(C11="",0,CHAR(39)&amp;C11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D11),D11,IF(D11="",0,CHAR(39)&amp;D11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E11),E11,IF(E11="",0,CHAR(39)&amp;E11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F11),F11,IF(F11="",0,CHAR(39)&amp;F11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G11),G11,IF(G11="",0,CHAR(39)&amp;G11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H11),H11,IF(H11="",0,CHAR(39)&amp;H11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I11),I11,IF(I11="",0,CHAR(39)&amp;I11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J11),J11,IF(J11="",0,CHAR(39)&amp;J11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K11),K11,IF(K11="",0,CHAR(39)&amp;K11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L11),L11,IF(L11="",0,CHAR(39)&amp;L11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M11),M11,IF(M11="",0,CHAR(39)&amp;M11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N11),N11,IF(N11="",0,CHAR(39)&amp;N11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O11),O11,IF(O11="",0,CHAR(39)&amp;O11&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="13"/>
       <c r="B12">
-        <f t="shared" si="2"/>
+        <f>SUM(H12:L12)</f>
         <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1478,23 +1426,23 @@
       <c r="J12">
         <v>10</v>
       </c>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R12" t="s">
-        <v>146</v>
-      </c>
-      <c r="T12" t="str">
-        <f t="shared" si="1"/>
-        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,0,0,'upgrade2','water,hydro'],</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="O12" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q12" t="e">
+        <f>"["&amp;IF(ISNUMBER(C12),C12,IF(C12="",0,CHAR(39)&amp;C12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D12),D12,IF(D12="",0,CHAR(39)&amp;D12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E12),E12,IF(E12="",0,CHAR(39)&amp;E12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F12),F12,IF(F12="",0,CHAR(39)&amp;F12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G12),G12,IF(G12="",0,CHAR(39)&amp;G12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H12),H12,IF(H12="",0,CHAR(39)&amp;H12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I12),I12,IF(I12="",0,CHAR(39)&amp;I12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J12),J12,IF(J12="",0,CHAR(39)&amp;J12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K12),K12,IF(K12="",0,CHAR(39)&amp;K12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L12),L12,IF(L12="",0,CHAR(39)&amp;L12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M12),M12,IF(M12="",0,CHAR(39)&amp;M12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N12),N12,IF(N12="",0,CHAR(39)&amp;N12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O12),O12,IF(O12="",0,CHAR(39)&amp;O12&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
       <c r="B13">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>SUM(H13:L13)</f>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
@@ -1515,82 +1463,82 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>5</v>
-      </c>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="R13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="O13" t="s">
         <v>53</v>
       </c>
-      <c r="T13" t="str">
-        <f t="shared" si="1"/>
-        <v>['anti',20,20,'Antimatter Chamber','REPAIR',10,0,0,0,5,0,0,0,0,'upgrade2','solar'],</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>66</v>
+      <c r="Q13" t="e">
+        <f>"["&amp;IF(ISNUMBER(C13),C13,IF(C13="",0,CHAR(39)&amp;C13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D13),D13,IF(D13="",0,CHAR(39)&amp;D13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E13),E13,IF(E13="",0,CHAR(39)&amp;E13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F13),F13,IF(F13="",0,CHAR(39)&amp;F13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G13),G13,IF(G13="",0,CHAR(39)&amp;G13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H13),H13,IF(H13="",0,CHAR(39)&amp;H13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I13),I13,IF(I13="",0,CHAR(39)&amp;I13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J13),J13,IF(J13="",0,CHAR(39)&amp;J13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K13),K13,IF(K13="",0,CHAR(39)&amp;K13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L13),L13,IF(L13="",0,CHAR(39)&amp;L13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M13),M13,IF(M13="",0,CHAR(39)&amp;M13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N13),N13,IF(N13="",0,CHAR(39)&amp;N13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O13),O13,IF(O13="",0,CHAR(39)&amp;O13&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="B14">
-        <f t="shared" si="2"/>
+        <f>SUM(H14:L14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>30</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="G14" t="s">
         <v>38</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="R14" t="s">
-        <v>79</v>
-      </c>
-      <c r="T14" t="str">
-        <f t="shared" si="1"/>
-        <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,0,0,'Allows you to explore space.','upgrade3','fab,med,anti'],</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="15"/>
+      <c r="M14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="O14" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" t="e">
+        <f>"["&amp;IF(ISNUMBER(C14),C14,IF(C14="",0,CHAR(39)&amp;C14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D14),D14,IF(D14="",0,CHAR(39)&amp;D14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E14),E14,IF(E14="",0,CHAR(39)&amp;E14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F14),F14,IF(F14="",0,CHAR(39)&amp;F14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G14),G14,IF(G14="",0,CHAR(39)&amp;G14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H14),H14,IF(H14="",0,CHAR(39)&amp;H14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I14),I14,IF(I14="",0,CHAR(39)&amp;I14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J14),J14,IF(J14="",0,CHAR(39)&amp;J14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K14),K14,IF(K14="",0,CHAR(39)&amp;K14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L14),L14,IF(L14="",0,CHAR(39)&amp;L14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M14),M14,IF(M14="",0,CHAR(39)&amp;M14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N14),N14,IF(N14="",0,CHAR(39)&amp;N14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O14),O14,IF(O14="",0,CHAR(39)&amp;O14&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="16"/>
       <c r="B15">
-        <f t="shared" si="2"/>
+        <f>SUM(H15:L15)</f>
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q15" s="8"/>
-      <c r="T15" t="str">
-        <f t="shared" si="1"/>
-        <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,0,0,'Lets you peek into the endless void of space.',0,0],</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
+        <v>73</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="N15" s="8"/>
+      <c r="Q15" t="e">
+        <f>"["&amp;IF(ISNUMBER(C15),C15,IF(C15="",0,CHAR(39)&amp;C15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D15),D15,IF(D15="",0,CHAR(39)&amp;D15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E15),E15,IF(E15="",0,CHAR(39)&amp;E15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F15),F15,IF(F15="",0,CHAR(39)&amp;F15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G15),G15,IF(G15="",0,CHAR(39)&amp;G15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H15),H15,IF(H15="",0,CHAR(39)&amp;H15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I15),I15,IF(I15="",0,CHAR(39)&amp;I15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J15),J15,IF(J15="",0,CHAR(39)&amp;J15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K15),K15,IF(K15="",0,CHAR(39)&amp;K15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L15),L15,IF(L15="",0,CHAR(39)&amp;L15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M15),M15,IF(M15="",0,CHAR(39)&amp;M15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N15),N15,IF(N15="",0,CHAR(39)&amp;N15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O15),O15,IF(O15="",0,CHAR(39)&amp;O15&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16"/>
       <c r="B16">
-        <f t="shared" si="2"/>
+        <f>SUM(H16:L16)</f>
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1600,915 +1548,620 @@
         <v>29</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="T16" t="str">
-        <f t="shared" si="1"/>
-        <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,0,0,'Travel to new locations!','req hazard on homebase only',0],</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
+        <v>104</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q16" t="e">
+        <f>"["&amp;IF(ISNUMBER(C16),C16,IF(C16="",0,CHAR(39)&amp;C16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D16),D16,IF(D16="",0,CHAR(39)&amp;D16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E16),E16,IF(E16="",0,CHAR(39)&amp;E16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F16),F16,IF(F16="",0,CHAR(39)&amp;F16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G16),G16,IF(G16="",0,CHAR(39)&amp;G16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H16),H16,IF(H16="",0,CHAR(39)&amp;H16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I16),I16,IF(I16="",0,CHAR(39)&amp;I16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J16),J16,IF(J16="",0,CHAR(39)&amp;J16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K16),K16,IF(K16="",0,CHAR(39)&amp;K16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L16),L16,IF(L16="",0,CHAR(39)&amp;L16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M16),M16,IF(M16="",0,CHAR(39)&amp;M16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N16),N16,IF(N16="",0,CHAR(39)&amp;N16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O16),O16,IF(O16="",0,CHAR(39)&amp;O16&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" s="16"/>
       <c r="B17">
-        <f t="shared" si="2"/>
+        <f>SUM(H17:L17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>39</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q17" s="8"/>
-      <c r="T17" t="str">
-        <f t="shared" si="1"/>
-        <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,0,0,'See available upgrades.',0,0],</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>67</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N17" s="8"/>
+      <c r="Q17" t="e">
+        <f>"["&amp;IF(ISNUMBER(C17),C17,IF(C17="",0,CHAR(39)&amp;C17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D17),D17,IF(D17="",0,CHAR(39)&amp;D17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E17),E17,IF(E17="",0,CHAR(39)&amp;E17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F17),F17,IF(F17="",0,CHAR(39)&amp;F17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G17),G17,IF(G17="",0,CHAR(39)&amp;G17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H17),H17,IF(H17="",0,CHAR(39)&amp;H17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I17),I17,IF(I17="",0,CHAR(39)&amp;I17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J17),J17,IF(J17="",0,CHAR(39)&amp;J17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K17),K17,IF(K17="",0,CHAR(39)&amp;K17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L17),L17,IF(L17="",0,CHAR(39)&amp;L17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M17),M17,IF(M17="",0,CHAR(39)&amp;M17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N17),N17,IF(N17="",0,CHAR(39)&amp;N17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O17),O17,IF(O17="",0,CHAR(39)&amp;O17&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="15"/>
       <c r="B18">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>SUM(H18:L18)</f>
+        <v>120</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18">
-        <v>15</v>
-      </c>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="T18" t="str">
-        <f t="shared" si="1"/>
-        <v>['mining',5,30,'Mining station','CAPTURE',0,0,0,0,0,0,15,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="H18">
+        <v>120</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="Q18" t="e">
+        <f>"["&amp;IF(ISNUMBER(C18),C18,IF(C18="",0,CHAR(39)&amp;C18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D18),D18,IF(D18="",0,CHAR(39)&amp;D18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E18),E18,IF(E18="",0,CHAR(39)&amp;E18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F18),F18,IF(F18="",0,CHAR(39)&amp;F18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G18),G18,IF(G18="",0,CHAR(39)&amp;G18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H18),H18,IF(H18="",0,CHAR(39)&amp;H18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I18),I18,IF(I18="",0,CHAR(39)&amp;I18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J18),J18,IF(J18="",0,CHAR(39)&amp;J18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K18),K18,IF(K18="",0,CHAR(39)&amp;K18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L18),L18,IF(L18="",0,CHAR(39)&amp;L18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M18),M18,IF(M18="",0,CHAR(39)&amp;M18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N18),N18,IF(N18="",0,CHAR(39)&amp;N18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O18),O18,IF(O18="",0,CHAR(39)&amp;O18&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="15"/>
       <c r="B19">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>SUM(H19:L19)</f>
+        <v>120</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="E19">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="O19">
-        <v>15</v>
-      </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="T19" t="str">
-        <f t="shared" si="1"/>
-        <v>['scrapyard',5,30,'Scrapyard','CAPTURE',0,0,0,0,0,0,0,15,0,0,0],</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="I19">
+        <v>120</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="Q19" t="e">
+        <f>"["&amp;IF(ISNUMBER(C19),C19,IF(C19="",0,CHAR(39)&amp;C19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D19),D19,IF(D19="",0,CHAR(39)&amp;D19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E19),E19,IF(E19="",0,CHAR(39)&amp;E19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F19),F19,IF(F19="",0,CHAR(39)&amp;F19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G19),G19,IF(G19="",0,CHAR(39)&amp;G19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H19),H19,IF(H19="",0,CHAR(39)&amp;H19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I19),I19,IF(I19="",0,CHAR(39)&amp;I19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J19),J19,IF(J19="",0,CHAR(39)&amp;J19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K19),K19,IF(K19="",0,CHAR(39)&amp;K19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L19),L19,IF(L19="",0,CHAR(39)&amp;L19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M19),M19,IF(M19="",0,CHAR(39)&amp;M19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N19),N19,IF(N19="",0,CHAR(39)&amp;N19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O19),O19,IF(O19="",0,CHAR(39)&amp;O19&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="15"/>
       <c r="B20">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>SUM(H20:L20)</f>
+        <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>36</v>
-      </c>
-      <c r="M20">
-        <v>5</v>
-      </c>
-      <c r="N20">
-        <v>5</v>
-      </c>
-      <c r="O20">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="T20" t="str">
-        <f t="shared" si="1"/>
-        <v>['data',5,30,'Data vault','CAPTURE',0,0,0,0,0,5,5,5,0,0,0],</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="J20">
+        <v>120</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="Q20" t="e">
+        <f>"["&amp;IF(ISNUMBER(C20),C20,IF(C20="",0,CHAR(39)&amp;C20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D20),D20,IF(D20="",0,CHAR(39)&amp;D20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E20),E20,IF(E20="",0,CHAR(39)&amp;E20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F20),F20,IF(F20="",0,CHAR(39)&amp;F20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G20),G20,IF(G20="",0,CHAR(39)&amp;G20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H20),H20,IF(H20="",0,CHAR(39)&amp;H20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I20),I20,IF(I20="",0,CHAR(39)&amp;I20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J20),J20,IF(J20="",0,CHAR(39)&amp;J20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K20),K20,IF(K20="",0,CHAR(39)&amp;K20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L20),L20,IF(L20="",0,CHAR(39)&amp;L20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M20),M20,IF(M20="",0,CHAR(39)&amp;M20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N20),N20,IF(N20="",0,CHAR(39)&amp;N20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O20),O20,IF(O20="",0,CHAR(39)&amp;O20&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A21" s="15"/>
       <c r="B21">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>SUM(H21:L21)</f>
+        <v>120</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="T21" t="str">
-        <f t="shared" si="1"/>
-        <v>['supply',5,30,'Supply depot','CAPTURE',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="K21">
+        <v>120</v>
+      </c>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="Q21" t="e">
+        <f>"["&amp;IF(ISNUMBER(C21),C21,IF(C21="",0,CHAR(39)&amp;C21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D21),D21,IF(D21="",0,CHAR(39)&amp;D21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E21),E21,IF(E21="",0,CHAR(39)&amp;E21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F21),F21,IF(F21="",0,CHAR(39)&amp;F21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G21),G21,IF(G21="",0,CHAR(39)&amp;G21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H21),H21,IF(H21="",0,CHAR(39)&amp;H21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I21),I21,IF(I21="",0,CHAR(39)&amp;I21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J21),J21,IF(J21="",0,CHAR(39)&amp;J21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K21),K21,IF(K21="",0,CHAR(39)&amp;K21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L21),L21,IF(L21="",0,CHAR(39)&amp;L21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M21),M21,IF(M21="",0,CHAR(39)&amp;M21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N21),N21,IF(N21="",0,CHAR(39)&amp;N21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O21),O21,IF(O21="",0,CHAR(39)&amp;O21&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="15"/>
       <c r="B22">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <f>SUM(H22:L22)</f>
+        <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="Q22" t="e">
+        <f>"["&amp;IF(ISNUMBER(C22),C22,IF(C22="",0,CHAR(39)&amp;C22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D22),D22,IF(D22="",0,CHAR(39)&amp;D22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E22),E22,IF(E22="",0,CHAR(39)&amp;E22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F22),F22,IF(F22="",0,CHAR(39)&amp;F22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G22),G22,IF(G22="",0,CHAR(39)&amp;G22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H22),H22,IF(H22="",0,CHAR(39)&amp;H22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I22),I22,IF(I22="",0,CHAR(39)&amp;I22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J22),J22,IF(J22="",0,CHAR(39)&amp;J22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K22),K22,IF(K22="",0,CHAR(39)&amp;K22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L22),L22,IF(L22="",0,CHAR(39)&amp;L22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M22),M22,IF(M22="",0,CHAR(39)&amp;M22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N22),N22,IF(N22="",0,CHAR(39)&amp;N22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O22),O22,IF(O22="",0,CHAR(39)&amp;O22&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A23" s="15"/>
+      <c r="B23">
+        <f>SUM(H23:L23)</f>
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="Q23" t="e">
+        <f>"["&amp;IF(ISNUMBER(C23),C23,IF(C23="",0,CHAR(39)&amp;C23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D23),D23,IF(D23="",0,CHAR(39)&amp;D23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E23),E23,IF(E23="",0,CHAR(39)&amp;E23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F23),F23,IF(F23="",0,CHAR(39)&amp;F23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G23),G23,IF(G23="",0,CHAR(39)&amp;G23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H23),H23,IF(H23="",0,CHAR(39)&amp;H23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I23),I23,IF(I23="",0,CHAR(39)&amp;I23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J23),J23,IF(J23="",0,CHAR(39)&amp;J23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K23),K23,IF(K23="",0,CHAR(39)&amp;K23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L23),L23,IF(L23="",0,CHAR(39)&amp;L23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M23),M23,IF(M23="",0,CHAR(39)&amp;M23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N23),N23,IF(N23="",0,CHAR(39)&amp;N23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O23),O23,IF(O23="",0,CHAR(39)&amp;O23&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A24" s="15"/>
+      <c r="B24">
+        <f>SUM(H24:L24)</f>
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="Q24" t="e">
+        <f>"["&amp;IF(ISNUMBER(C24),C24,IF(C24="",0,CHAR(39)&amp;C24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D24),D24,IF(D24="",0,CHAR(39)&amp;D24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E24),E24,IF(E24="",0,CHAR(39)&amp;E24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F24),F24,IF(F24="",0,CHAR(39)&amp;F24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G24),G24,IF(G24="",0,CHAR(39)&amp;G24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H24),H24,IF(H24="",0,CHAR(39)&amp;H24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I24),I24,IF(I24="",0,CHAR(39)&amp;I24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J24),J24,IF(J24="",0,CHAR(39)&amp;J24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K24),K24,IF(K24="",0,CHAR(39)&amp;K24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L24),L24,IF(L24="",0,CHAR(39)&amp;L24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M24),M24,IF(M24="",0,CHAR(39)&amp;M24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N24),N24,IF(N24="",0,CHAR(39)&amp;N24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O24),O24,IF(O24="",0,CHAR(39)&amp;O24&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="15"/>
+      <c r="B25">
+        <f>SUM(H25:L25)</f>
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="Q25" t="e">
+        <f>"["&amp;IF(ISNUMBER(C25),C25,IF(C25="",0,CHAR(39)&amp;C25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D25),D25,IF(D25="",0,CHAR(39)&amp;D25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E25),E25,IF(E25="",0,CHAR(39)&amp;E25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F25),F25,IF(F25="",0,CHAR(39)&amp;F25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G25),G25,IF(G25="",0,CHAR(39)&amp;G25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H25),H25,IF(H25="",0,CHAR(39)&amp;H25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I25),I25,IF(I25="",0,CHAR(39)&amp;I25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J25),J25,IF(J25="",0,CHAR(39)&amp;J25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K25),K25,IF(K25="",0,CHAR(39)&amp;K25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L25),L25,IF(L25="",0,CHAR(39)&amp;L25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M25),M25,IF(M25="",0,CHAR(39)&amp;M25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N25),N25,IF(N25="",0,CHAR(39)&amp;N25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O25),O25,IF(O25="",0,CHAR(39)&amp;O25&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26" s="15"/>
+      <c r="B26">
+        <f>SUM(H26:L26)</f>
+        <v>80</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26">
         <v>40</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" t="s">
-        <v>36</v>
-      </c>
-      <c r="L22">
-        <v>15</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="T22" t="str">
-        <f t="shared" si="1"/>
-        <v>['fusion',5,40,'Fusion core','CAPTURE',0,0,0,0,15,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23">
-        <v>5</v>
-      </c>
-      <c r="E23">
-        <v>30</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23">
-        <v>10</v>
-      </c>
-      <c r="O23">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="T23" t="str">
-        <f t="shared" si="1"/>
-        <v>['alloy',5,30,'Alloy plant','CAPTURE',0,0,0,0,0,0,10,5,0,0,0],</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
-      <c r="B24">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24">
-        <v>5</v>
-      </c>
-      <c r="E24">
-        <v>40</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" t="s">
-        <v>36</v>
-      </c>
-      <c r="L24">
-        <v>5</v>
-      </c>
-      <c r="M24">
-        <v>5</v>
-      </c>
-      <c r="O24">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="T24" t="str">
-        <f t="shared" si="1"/>
-        <v>['research',5,40,'Research lab','CAPTURE',0,0,0,0,5,5,0,5,0,0,0],</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
-      <c r="B25">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25">
-        <v>20</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" t="s">
-        <v>85</v>
-      </c>
-      <c r="H25">
-        <v>120</v>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="T25" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestenergy',0,20,'Energy cells','CLAIM',120,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26">
-        <v>20</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
-      </c>
-      <c r="I26">
-        <v>120</v>
-      </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="T26" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestwater',0,20,'Ice blocks','CLAIM',0,120,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="L26">
+        <v>80</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="Q26" t="e">
+        <f>"["&amp;IF(ISNUMBER(C26),C26,IF(C26="",0,CHAR(39)&amp;C26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D26),D26,IF(D26="",0,CHAR(39)&amp;D26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E26),E26,IF(E26="",0,CHAR(39)&amp;E26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F26),F26,IF(F26="",0,CHAR(39)&amp;F26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G26),G26,IF(G26="",0,CHAR(39)&amp;G26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H26),H26,IF(H26="",0,CHAR(39)&amp;H26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I26),I26,IF(I26="",0,CHAR(39)&amp;I26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J26),J26,IF(J26="",0,CHAR(39)&amp;J26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K26),K26,IF(K26="",0,CHAR(39)&amp;K26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L26),L26,IF(L26="",0,CHAR(39)&amp;L26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M26),M26,IF(M26="",0,CHAR(39)&amp;M26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N26),N26,IF(N26="",0,CHAR(39)&amp;N26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O26),O26,IF(O26="",0,CHAR(39)&amp;O26&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="15"/>
       <c r="B27">
-        <f t="shared" si="2"/>
-        <v>120</v>
+        <f>SUM(H27:L27)</f>
+        <v>0</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
-      </c>
-      <c r="J27">
-        <v>120</v>
-      </c>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="T27" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestfood',0,20,'Nutrient packs','CLAIM',0,0,120,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
+        <v>95</v>
+      </c>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="Q27" t="e">
+        <f>"["&amp;IF(ISNUMBER(C27),C27,IF(C27="",0,CHAR(39)&amp;C27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D27),D27,IF(D27="",0,CHAR(39)&amp;D27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E27),E27,IF(E27="",0,CHAR(39)&amp;E27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F27),F27,IF(F27="",0,CHAR(39)&amp;F27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G27),G27,IF(G27="",0,CHAR(39)&amp;G27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H27),H27,IF(H27="",0,CHAR(39)&amp;H27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I27),I27,IF(I27="",0,CHAR(39)&amp;I27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J27),J27,IF(J27="",0,CHAR(39)&amp;J27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K27),K27,IF(K27="",0,CHAR(39)&amp;K27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L27),L27,IF(L27="",0,CHAR(39)&amp;L27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M27),M27,IF(M27="",0,CHAR(39)&amp;M27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N27),N27,IF(N27="",0,CHAR(39)&amp;N27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O27),O27,IF(O27="",0,CHAR(39)&amp;O27&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="15"/>
       <c r="B28">
-        <f t="shared" si="2"/>
-        <v>120</v>
+        <f>SUM(H28:L28)</f>
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E28">
         <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s">
+        <v>95</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="Q28" t="e">
+        <f>"["&amp;IF(ISNUMBER(C28),C28,IF(C28="",0,CHAR(39)&amp;C28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D28),D28,IF(D28="",0,CHAR(39)&amp;D28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E28),E28,IF(E28="",0,CHAR(39)&amp;E28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F28),F28,IF(F28="",0,CHAR(39)&amp;F28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G28),G28,IF(G28="",0,CHAR(39)&amp;G28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H28),H28,IF(H28="",0,CHAR(39)&amp;H28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I28),I28,IF(I28="",0,CHAR(39)&amp;I28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J28),J28,IF(J28="",0,CHAR(39)&amp;J28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K28),K28,IF(K28="",0,CHAR(39)&amp;K28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L28),L28,IF(L28="",0,CHAR(39)&amp;L28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M28),M28,IF(M28="",0,CHAR(39)&amp;M28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N28),N28,IF(N28="",0,CHAR(39)&amp;N28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O28),O28,IF(O28="",0,CHAR(39)&amp;O28&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="15"/>
+      <c r="B29">
+        <f>SUM(H29:L29)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29">
+        <v>50</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G29" t="s">
+        <v>95</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="Q29" t="e">
+        <f>"["&amp;IF(ISNUMBER(C29),C29,IF(C29="",0,CHAR(39)&amp;C29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D29),D29,IF(D29="",0,CHAR(39)&amp;D29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E29),E29,IF(E29="",0,CHAR(39)&amp;E29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F29),F29,IF(F29="",0,CHAR(39)&amp;F29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G29),G29,IF(G29="",0,CHAR(39)&amp;G29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H29),H29,IF(H29="",0,CHAR(39)&amp;H29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I29),I29,IF(I29="",0,CHAR(39)&amp;I29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J29),J29,IF(J29="",0,CHAR(39)&amp;J29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K29),K29,IF(K29="",0,CHAR(39)&amp;K29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L29),L29,IF(L29="",0,CHAR(39)&amp;L29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M29),M29,IF(M29="",0,CHAR(39)&amp;M29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N29),N29,IF(N29="",0,CHAR(39)&amp;N29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O29),O29,IF(O29="",0,CHAR(39)&amp;O29&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30" s="15"/>
+      <c r="B30">
+        <f>SUM(H30:L30)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30">
+        <v>70</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" t="s">
+        <v>95</v>
+      </c>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="Q30" t="e">
+        <f>"["&amp;IF(ISNUMBER(C30),C30,IF(C30="",0,CHAR(39)&amp;C30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D30),D30,IF(D30="",0,CHAR(39)&amp;D30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E30),E30,IF(E30="",0,CHAR(39)&amp;E30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F30),F30,IF(F30="",0,CHAR(39)&amp;F30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G30),G30,IF(G30="",0,CHAR(39)&amp;G30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H30),H30,IF(H30="",0,CHAR(39)&amp;H30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I30),I30,IF(I30="",0,CHAR(39)&amp;I30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J30),J30,IF(J30="",0,CHAR(39)&amp;J30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K30),K30,IF(K30="",0,CHAR(39)&amp;K30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L30),L30,IF(L30="",0,CHAR(39)&amp;L30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M30),M30,IF(M30="",0,CHAR(39)&amp;M30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N30),N30,IF(N30="",0,CHAR(39)&amp;N30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O30),O30,IF(O30="",0,CHAR(39)&amp;O30&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31">
+        <f>SUM(H31:L31)</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="K28">
-        <v>120</v>
-      </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="T28" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestparts',0,20,'Parts box','CLAIM',0,0,0,120,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" t="s">
+        <v>96</v>
+      </c>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="Q31" t="e">
+        <f>"["&amp;IF(ISNUMBER(C31),C31,IF(C31="",0,CHAR(39)&amp;C31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D31),D31,IF(D31="",0,CHAR(39)&amp;D31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E31),E31,IF(E31="",0,CHAR(39)&amp;E31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F31),F31,IF(F31="",0,CHAR(39)&amp;F31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G31),G31,IF(G31="",0,CHAR(39)&amp;G31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H31),H31,IF(H31="",0,CHAR(39)&amp;H31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I31),I31,IF(I31="",0,CHAR(39)&amp;I31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J31),J31,IF(J31="",0,CHAR(39)&amp;J31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K31),K31,IF(K31="",0,CHAR(39)&amp;K31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L31),L31,IF(L31="",0,CHAR(39)&amp;L31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M31),M31,IF(M31="",0,CHAR(39)&amp;M31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N31),N31,IF(N31="",0,CHAR(39)&amp;N31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O31),O31,IF(O31="",0,CHAR(39)&amp;O31&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32" s="13"/>
+      <c r="B32">
+        <f>SUM(H32:L32)</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" t="s">
+        <v>96</v>
+      </c>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="Q32" t="e">
+        <f>"["&amp;IF(ISNUMBER(C32),C32,IF(C32="",0,CHAR(39)&amp;C32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D32),D32,IF(D32="",0,CHAR(39)&amp;D32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E32),E32,IF(E32="",0,CHAR(39)&amp;E32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F32),F32,IF(F32="",0,CHAR(39)&amp;F32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G32),G32,IF(G32="",0,CHAR(39)&amp;G32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H32),H32,IF(H32="",0,CHAR(39)&amp;H32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I32),I32,IF(I32="",0,CHAR(39)&amp;I32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J32),J32,IF(J32="",0,CHAR(39)&amp;J32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K32),K32,IF(K32="",0,CHAR(39)&amp;K32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L32),L32,IF(L32="",0,CHAR(39)&amp;L32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M32),M32,IF(M32="",0,CHAR(39)&amp;M32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N32),N32,IF(N32="",0,CHAR(39)&amp;N32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O32),O32,IF(O32="",0,CHAR(39)&amp;O32&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A33" s="13"/>
+      <c r="B33">
+        <f>SUM(H33:L33)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" t="s">
+        <v>96</v>
+      </c>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="Q33" t="e">
+        <f>"["&amp;IF(ISNUMBER(C33),C33,IF(C33="",0,CHAR(39)&amp;C33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D33),D33,IF(D33="",0,CHAR(39)&amp;D33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E33),E33,IF(E33="",0,CHAR(39)&amp;E33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F33),F33,IF(F33="",0,CHAR(39)&amp;F33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G33),G33,IF(G33="",0,CHAR(39)&amp;G33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H33),H33,IF(H33="",0,CHAR(39)&amp;H33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I33),I33,IF(I33="",0,CHAR(39)&amp;I33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J33),J33,IF(J33="",0,CHAR(39)&amp;J33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K33),K33,IF(K33="",0,CHAR(39)&amp;K33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L33),L33,IF(L33="",0,CHAR(39)&amp;L33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M33),M33,IF(M33="",0,CHAR(39)&amp;M33&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34" s="13"/>
+      <c r="B34">
+        <f>SUM(H34:L34)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G34" t="s">
+        <v>96</v>
+      </c>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="Q34" t="e">
+        <f>"["&amp;IF(ISNUMBER(C34),C34,IF(C34="",0,CHAR(39)&amp;C34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D34),D34,IF(D34="",0,CHAR(39)&amp;D34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E34),E34,IF(E34="",0,CHAR(39)&amp;E34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F34),F34,IF(F34="",0,CHAR(39)&amp;F34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G34),G34,IF(G34="",0,CHAR(39)&amp;G34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H34),H34,IF(H34="",0,CHAR(39)&amp;H34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I34),I34,IF(I34="",0,CHAR(39)&amp;I34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J34),J34,IF(J34="",0,CHAR(39)&amp;J34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K34),K34,IF(K34="",0,CHAR(39)&amp;K34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L34),L34,IF(L34="",0,CHAR(39)&amp;L34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M34),M34,IF(M34="",0,CHAR(39)&amp;M34&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35" s="13"/>
+      <c r="B35">
+        <f>SUM(H35:L35)</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" t="s">
+        <v>96</v>
+      </c>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="Q35" t="e">
+        <f>"["&amp;IF(ISNUMBER(C35),C35,IF(C35="",0,CHAR(39)&amp;C35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D35),D35,IF(D35="",0,CHAR(39)&amp;D35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E35),E35,IF(E35="",0,CHAR(39)&amp;E35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F35),F35,IF(F35="",0,CHAR(39)&amp;F35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G35),G35,IF(G35="",0,CHAR(39)&amp;G35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H35),H35,IF(H35="",0,CHAR(39)&amp;H35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I35),I35,IF(I35="",0,CHAR(39)&amp;I35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J35),J35,IF(J35="",0,CHAR(39)&amp;J35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K35),K35,IF(K35="",0,CHAR(39)&amp;K35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L35),L35,IF(L35="",0,CHAR(39)&amp;L35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M35),M35,IF(M35="",0,CHAR(39)&amp;M35&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36" s="13"/>
+      <c r="B36">
+        <f>SUM(H36:L36)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="G29" t="s">
-        <v>85</v>
-      </c>
-      <c r="H29">
-        <v>10</v>
-      </c>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="T29" t="str">
-        <f t="shared" si="1"/>
-        <v>['smallenergy',0,0,'Small battery','CLAIM',10,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G30" t="s">
-        <v>85</v>
-      </c>
-      <c r="I30">
-        <v>10</v>
-      </c>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="T30" t="str">
-        <f t="shared" si="1"/>
-        <v>['smallwater',0,0,'Small water bottle','CLAIM',0,10,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
-      <c r="B31">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" t="s">
-        <v>85</v>
-      </c>
-      <c r="J31">
-        <v>10</v>
-      </c>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="T31" t="str">
-        <f t="shared" si="1"/>
-        <v>['smallfood',0,0,'Small candy bar','CLAIM',0,0,10,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
-      <c r="B32">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G32" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32">
-        <v>10</v>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="T32" t="str">
-        <f t="shared" si="1"/>
-        <v>['smallparts',0,0,'Small circuits','CLAIM',0,0,0,10,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
-      <c r="B33">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33">
-        <v>40</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" t="s">
-        <v>85</v>
-      </c>
-      <c r="L33">
-        <v>80</v>
-      </c>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="T33" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestantimatter',0,40,'Antimatter traces','CLAIM',0,0,0,0,80,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
-      <c r="B34">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34">
-        <v>40</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" t="s">
-        <v>85</v>
-      </c>
-      <c r="M34">
-        <v>80</v>
-      </c>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="T34" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestcoolant',0,40,'Coolant remains','CLAIM',0,0,0,0,0,80,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
-      <c r="B35">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35">
-        <v>40</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G35" t="s">
-        <v>85</v>
-      </c>
-      <c r="N35">
-        <v>80</v>
-      </c>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="T35" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestmineral',0,40,'Mineral residue','CLAIM',0,0,0,0,0,0,80,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
-      <c r="B36">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36">
-        <v>40</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="G36" t="s">
-        <v>85</v>
-      </c>
-      <c r="O36">
-        <v>80</v>
-      </c>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="T36" t="str">
-        <f t="shared" si="1"/>
-        <v>['chestsalvage',0,40,'Salvage pack','CLAIM',0,0,0,0,0,0,0,80,0,0,0],</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="Q36" t="e">
+        <f>"["&amp;IF(ISNUMBER(C36),C36,IF(C36="",0,CHAR(39)&amp;C36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D36),D36,IF(D36="",0,CHAR(39)&amp;D36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E36),E36,IF(E36="",0,CHAR(39)&amp;E36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F36),F36,IF(F36="",0,CHAR(39)&amp;F36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G36),G36,IF(G36="",0,CHAR(39)&amp;G36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H36),H36,IF(H36="",0,CHAR(39)&amp;H36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I36),I36,IF(I36="",0,CHAR(39)&amp;I36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J36),J36,IF(J36="",0,CHAR(39)&amp;J36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K36),K36,IF(K36="",0,CHAR(39)&amp;K36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L36),L36,IF(L36="",0,CHAR(39)&amp;L36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M36),M36,IF(M36="",0,CHAR(39)&amp;M36&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37" s="13"/>
       <c r="B37">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>91</v>
-      </c>
+        <f>SUM(H37:L37)</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="F37" s="9"/>
       <c r="G37" t="s">
-        <v>106</v>
-      </c>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="T37" t="str">
-        <f t="shared" si="1"/>
-        <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
+        <v>96</v>
+      </c>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="Q37" t="e">
+        <f>"["&amp;IF(ISNUMBER(C37),C37,IF(C37="",0,CHAR(39)&amp;C37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D37),D37,IF(D37="",0,CHAR(39)&amp;D37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E37),E37,IF(E37="",0,CHAR(39)&amp;E37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F37),F37,IF(F37="",0,CHAR(39)&amp;F37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G37),G37,IF(G37="",0,CHAR(39)&amp;G37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H37),H37,IF(H37="",0,CHAR(39)&amp;H37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I37),I37,IF(I37="",0,CHAR(39)&amp;I37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J37),J37,IF(J37="",0,CHAR(39)&amp;J37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K37),K37,IF(K37="",0,CHAR(39)&amp;K37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L37),L37,IF(L37="",0,CHAR(39)&amp;L37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M37),M37,IF(M37="",0,CHAR(39)&amp;M37&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38" s="13"/>
       <c r="B38">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38">
-        <v>20</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>92</v>
-      </c>
+        <f>SUM(H38:L38)</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="F38" s="9"/>
       <c r="G38" t="s">
-        <v>106</v>
-      </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="T38" t="str">
-        <f t="shared" si="1"/>
-        <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
-      <c r="B39">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39">
-        <v>50</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G39" t="s">
-        <v>106</v>
-      </c>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="T39" t="str">
-        <f t="shared" si="1"/>
-        <v>['door_hard',0,50,'Reinforced door','HACK',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
-      <c r="B40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40">
-        <v>70</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="T40" t="str">
-        <f t="shared" si="1"/>
-        <v>['door_extreme',0,70,'High security door',0,0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A41" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C41" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" t="s">
-        <v>107</v>
-      </c>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9"/>
-      <c r="T41" t="str">
-        <f t="shared" si="1"/>
-        <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
-      <c r="B42">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42">
-        <v>10</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G42" t="s">
-        <v>107</v>
-      </c>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="T42" t="str">
-        <f t="shared" si="1"/>
-        <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E43">
-        <v>10</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G43" t="s">
-        <v>107</v>
-      </c>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
-      <c r="T43" t="str">
-        <f t="shared" ref="T43:T48" si="3">"["&amp;IF(ISNUMBER(C43),C43,IF(C43="",0,CHAR(39)&amp;C43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D43),D43,IF(D43="",0,CHAR(39)&amp;D43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E43),E43,IF(E43="",0,CHAR(39)&amp;E43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F43),F43,IF(F43="",0,CHAR(39)&amp;F43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G43),G43,IF(G43="",0,CHAR(39)&amp;G43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H43),H43,IF(H43="",0,CHAR(39)&amp;H43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I43),I43,IF(I43="",0,CHAR(39)&amp;I43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J43),J43,IF(J43="",0,CHAR(39)&amp;J43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K43),K43,IF(K43="",0,CHAR(39)&amp;K43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L43),L43,IF(L43="",0,CHAR(39)&amp;L43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M43),M43,IF(M43="",0,CHAR(39)&amp;M43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N43),N43,IF(N43="",0,CHAR(39)&amp;N43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O43),O43,IF(O43="",0,CHAR(39)&amp;O43&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P43),P43,IF(P43="",0,CHAR(39)&amp;P43&amp;CHAR(39)))&amp;"],"</f>
-        <v>['sink',0,10,'Sink','RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
-      <c r="B44">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E44">
-        <v>10</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G44" t="s">
-        <v>107</v>
-      </c>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
-      <c r="T44" t="str">
-        <f t="shared" si="3"/>
-        <v>['shower',0,10,'Shower','RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E45">
-        <v>10</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G45" t="s">
-        <v>107</v>
-      </c>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="T45" t="str">
-        <f t="shared" si="3"/>
-        <v>['sofa',0,10,'Sofa','RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
-      <c r="B46">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E46">
-        <v>10</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="G46" t="s">
-        <v>107</v>
-      </c>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
-      <c r="T46" t="str">
-        <f t="shared" si="3"/>
-        <v>['table',0,10,'Table','RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
-      <c r="B47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" t="s">
-        <v>107</v>
-      </c>
-      <c r="P47" s="9"/>
-      <c r="Q47" s="9"/>
-      <c r="T47" t="str">
-        <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" t="s">
-        <v>107</v>
-      </c>
-      <c r="P48" s="9"/>
-      <c r="Q48" s="9"/>
-      <c r="T48" t="str">
-        <f t="shared" si="3"/>
-        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="Q38" t="e">
+        <f>"["&amp;IF(ISNUMBER(C38),C38,IF(C38="",0,CHAR(39)&amp;C38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D38),D38,IF(D38="",0,CHAR(39)&amp;D38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E38),E38,IF(E38="",0,CHAR(39)&amp;E38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F38),F38,IF(F38="",0,CHAR(39)&amp;F38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G38),G38,IF(G38="",0,CHAR(39)&amp;G38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H38),H38,IF(H38="",0,CHAR(39)&amp;H38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I38),I38,IF(I38="",0,CHAR(39)&amp;I38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J38),J38,IF(J38="",0,CHAR(39)&amp;J38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K38),K38,IF(K38="",0,CHAR(39)&amp;K38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L38),L38,IF(L38="",0,CHAR(39)&amp;L38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M38),M38,IF(M38="",0,CHAR(39)&amp;M38&amp;CHAR(39)))&amp;"],"</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A41:A48"/>
+  <mergeCells count="5">
+    <mergeCell ref="A31:A38"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="A4:A13"/>
-    <mergeCell ref="A18:A40"/>
-    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="A18:A30"/>
     <mergeCell ref="A14:A17"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C41:C1048576 C1:C17">
+  <conditionalFormatting sqref="C31:C1048576 C1:C17">
     <cfRule type="duplicateValues" dxfId="10" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:O2 T2:U2">
+  <conditionalFormatting sqref="Q2:R2 D2:L2">
     <cfRule type="duplicateValues" dxfId="9" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E66">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="F31:F38">
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M31:N38">
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:O3">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:P2">
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E56">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2519,45 +2172,27 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F48">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P3">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P41:Q48">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:R3">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:S2">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="97.44140625" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="97.453125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="97.44140625" style="10"/>
+    <col min="1" max="16384" width="97.453125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2566,17 +2201,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="7.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
+    <col min="5" max="6" width="7.36328125" customWidth="1"/>
+    <col min="7" max="7" width="14.36328125" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -2648,7 +2283,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -2696,7 +2331,7 @@
         <v>["terminal","delay","question","pretty","action","energy","food","water","parts","metals","titanium","alloy"],</v>
       </c>
     </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B4">
         <f>SUM(E4:AA4)</f>
         <v>55</v>
@@ -2728,7 +2363,7 @@
         <v>["reactor",15,0,"Reactor","REPAIR",40,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B5">
         <f t="shared" ref="B5:B31" si="1">SUM(E5:AA5)</f>
         <v>55</v>
@@ -2764,7 +2399,7 @@
         <v xml:space="preserve"> * @property {number} solar</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B6">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -2803,7 +2438,7 @@
         <v xml:space="preserve"> * @property {number} hydro</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B7">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2839,7 +2474,7 @@
         <v xml:space="preserve"> * @property {number} water</v>
       </c>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B8">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2878,7 +2513,7 @@
         <v xml:space="preserve"> * @property {number} cargo</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B9">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -2914,7 +2549,7 @@
         <v xml:space="preserve"> * @property {number} comms</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B10">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -2953,7 +2588,7 @@
         <v xml:space="preserve"> * @property {number} fab</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B11">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2989,7 +2624,7 @@
         <v xml:space="preserve"> * @property {number} med</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B12">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3028,7 +2663,7 @@
         <v xml:space="preserve"> * @property {number} life</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
       <c r="B13">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -3064,7 +2699,7 @@
         <v xml:space="preserve"> * @property {number} machine</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
       <c r="C14" t="str">
         <f t="shared" si="2"/>
         <v>s</v>
@@ -3087,7 +2722,7 @@
         <v xml:space="preserve"> * @property {number} shuttle</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
       <c r="C15" t="str">
         <f t="shared" si="2"/>
         <v>a</v>
@@ -3110,7 +2745,7 @@
         <v xml:space="preserve"> * @property {number} access</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
       <c r="C16" t="str">
         <f t="shared" si="2"/>
         <v>d</v>
@@ -3133,7 +2768,7 @@
         <v xml:space="preserve"> * @property {number} door</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B17">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3175,7 +2810,7 @@
         <v xml:space="preserve"> * @property {number} mining</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B18">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3214,7 +2849,7 @@
         <v xml:space="preserve"> * @property {number} scrapyard</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B19">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3259,7 +2894,7 @@
         <v xml:space="preserve"> * @property {number} data</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B20">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -3301,7 +2936,7 @@
         <v xml:space="preserve"> * @property {number} supply</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B21">
         <f t="shared" si="1"/>
         <v>140</v>
@@ -3343,7 +2978,7 @@
         <v xml:space="preserve"> * @property {number} fusion</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B22">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -3382,7 +3017,7 @@
         <v xml:space="preserve"> * @property {number} alloy</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B23">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3424,7 +3059,7 @@
         <v xml:space="preserve"> * @property {number} research</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B24">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3434,7 +3069,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3444,7 +3079,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3454,7 +3089,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3464,7 +3099,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3474,7 +3109,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3484,7 +3119,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3494,7 +3129,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="1"/>
         <v>0</v>

--- a/docs/relay/design/scripting.xlsx
+++ b/docs/relay/design/scripting.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\js\games\docs\relay\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A9362A-E0E2-45F5-811D-C5430AEBCA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheetwithani" sheetId="3" r:id="rId1"/>
     <sheet name="conventions" sheetId="4" r:id="rId2"/>
     <sheet name="bad" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="151">
   <si>
     <t>firstletter</t>
   </si>
@@ -469,13 +470,55 @@
     <t>water,hydro</t>
   </si>
   <si>
-    <t>chestanti</t>
+    <t>Antimatter residue</t>
+  </si>
+  <si>
+    <t>Antimatter deposit</t>
+  </si>
+  <si>
+    <t>Antimatter vein</t>
+  </si>
+  <si>
+    <t>anti3</t>
+  </si>
+  <si>
+    <t>anti5</t>
+  </si>
+  <si>
+    <t>anti8</t>
+  </si>
+  <si>
+    <t>anti10</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>b||q</t>
+  </si>
+  <si>
+    <t>shuttleHome</t>
+  </si>
+  <si>
+    <t>will turn to shuttle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -485,7 +528,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,6 +589,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -559,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -591,6 +640,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,6 +665,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -689,16 +749,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1000,26 +1050,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.90625" customWidth="1"/>
-    <col min="2" max="2" width="4.08984375" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="5.1796875" customWidth="1"/>
+    <col min="4" max="4" width="5.21875" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="20.36328125" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" customWidth="1"/>
-    <col min="8" max="12" width="7.08984375" customWidth="1"/>
-    <col min="13" max="13" width="30.81640625" customWidth="1"/>
-    <col min="14" max="14" width="15.1796875" customWidth="1"/>
-    <col min="15" max="15" width="12.1796875" customWidth="1"/>
-    <col min="16" max="16" width="15.1796875" customWidth="1"/>
-    <col min="17" max="17" width="15.36328125" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="13" width="7.109375" customWidth="1"/>
+    <col min="14" max="14" width="30.77734375" customWidth="1"/>
+    <col min="15" max="15" width="15.21875" customWidth="1"/>
+    <col min="16" max="16" width="12.21875" customWidth="1"/>
+    <col min="17" max="17" width="15.21875" customWidth="1"/>
+    <col min="18" max="18" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="H1" s="14" t="s">
         <v>60</v>
       </c>
@@ -1029,19 +1079,28 @@
       <c r="L1" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="N1" t="s">
         <v>82</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>65</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>107</v>
+      </c>
+      <c r="E2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" t="s">
+        <v>147</v>
       </c>
       <c r="H2" s="2" t="str">
         <f>LEFT(H3,1)</f>
@@ -1063,11 +1122,12 @@
         <f t="shared" si="0"/>
         <v>a</v>
       </c>
-      <c r="P2" t="s">
+      <c r="M2" s="17"/>
+      <c r="Q2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -1101,26 +1161,29 @@
       <c r="L3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" t="s">
         <v>84</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="Q3" t="e">
-        <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R3" t="str">
+        <f>"["&amp;IF(ISNUMBER(C3),C3,IF(C3="",0,CHAR(39)&amp;C3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D3),D3,IF(D3="",0,CHAR(39)&amp;D3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E3),E3,IF(E3="",0,CHAR(39)&amp;E3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F3),F3,IF(F3="",0,CHAR(39)&amp;F3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G3),G3,IF(G3="",0,CHAR(39)&amp;G3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H3),H3,IF(H3="",0,CHAR(39)&amp;H3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I3),I3,IF(I3="",0,CHAR(39)&amp;I3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J3),J3,IF(J3="",0,CHAR(39)&amp;J3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K3),K3,IF(K3="",0,CHAR(39)&amp;K3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L3),L3,IF(L3="",0,CHAR(39)&amp;L3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M3),M3,IF(M3="",0,CHAR(39)&amp;M3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N3),N3,IF(N3="",0,CHAR(39)&amp;N3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O3),O3,IF(O3="",0,CHAR(39)&amp;O3&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P3),P3,IF(P3="",0,CHAR(39)&amp;P3&amp;CHAR(39)))&amp;"],"</f>
+        <v>['terminal','delay','bucket','pretty','action','energy','water','food','parts','antimatter','cost','description','note','prereq'],</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>62</v>
       </c>
       <c r="B4">
-        <f>SUM(H4:L4)</f>
+        <f t="shared" ref="B4:B43" si="1">SUM(H4:L4)</f>
         <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1141,19 +1204,19 @@
       <c r="H4">
         <v>50</v>
       </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="4"/>
+      <c r="O4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" t="e">
-        <f>"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R4" t="str">
+        <f>"["&amp;IF(ISNUMBER(C4),C4,IF(C4="",0,CHAR(39)&amp;C4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D4),D4,IF(D4="",0,CHAR(39)&amp;D4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E4),E4,IF(E4="",0,CHAR(39)&amp;E4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F4),F4,IF(F4="",0,CHAR(39)&amp;F4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G4),G4,IF(G4="",0,CHAR(39)&amp;G4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H4),H4,IF(H4="",0,CHAR(39)&amp;H4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I4),I4,IF(I4="",0,CHAR(39)&amp;I4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J4),J4,IF(J4="",0,CHAR(39)&amp;J4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K4),K4,IF(K4="",0,CHAR(39)&amp;K4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L4),L4,IF(L4="",0,CHAR(39)&amp;L4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M4),M4,IF(M4="",0,CHAR(39)&amp;M4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N4),N4,IF(N4="",0,CHAR(39)&amp;N4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O4),O4,IF(O4="",0,CHAR(39)&amp;O4&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P4),P4,IF(P4="",0,CHAR(39)&amp;P4&amp;CHAR(39)))&amp;"],"</f>
+        <v>['reactor',15,0,'Reactor','REPAIR',50,0,0,0,0,0,0,'base',0],</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="13"/>
       <c r="B5">
-        <f>SUM(H5:L5)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1174,22 +1237,22 @@
       <c r="H5">
         <v>30</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="5"/>
+      <c r="O5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>1</v>
       </c>
-      <c r="Q5" t="e">
-        <f>"["&amp;IF(ISNUMBER(C5),C5,IF(C5="",0,CHAR(39)&amp;C5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D5),D5,IF(D5="",0,CHAR(39)&amp;D5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E5),E5,IF(E5="",0,CHAR(39)&amp;E5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F5),F5,IF(F5="",0,CHAR(39)&amp;F5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G5),G5,IF(G5="",0,CHAR(39)&amp;G5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H5),H5,IF(H5="",0,CHAR(39)&amp;H5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I5),I5,IF(I5="",0,CHAR(39)&amp;I5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J5),J5,IF(J5="",0,CHAR(39)&amp;J5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K5),K5,IF(K5="",0,CHAR(39)&amp;K5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L5),L5,IF(L5="",0,CHAR(39)&amp;L5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M5),M5,IF(M5="",0,CHAR(39)&amp;M5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N5),N5,IF(N5="",0,CHAR(39)&amp;N5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O5),O5,IF(O5="",0,CHAR(39)&amp;O5&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R43" si="2">"["&amp;IF(ISNUMBER(C5),C5,IF(C5="",0,CHAR(39)&amp;C5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D5),D5,IF(D5="",0,CHAR(39)&amp;D5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E5),E5,IF(E5="",0,CHAR(39)&amp;E5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F5),F5,IF(F5="",0,CHAR(39)&amp;F5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G5),G5,IF(G5="",0,CHAR(39)&amp;G5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H5),H5,IF(H5="",0,CHAR(39)&amp;H5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I5),I5,IF(I5="",0,CHAR(39)&amp;I5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J5),J5,IF(J5="",0,CHAR(39)&amp;J5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K5),K5,IF(K5="",0,CHAR(39)&amp;K5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L5),L5,IF(L5="",0,CHAR(39)&amp;L5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M5),M5,IF(M5="",0,CHAR(39)&amp;M5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N5),N5,IF(N5="",0,CHAR(39)&amp;N5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O5),O5,IF(O5="",0,CHAR(39)&amp;O5&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P5),P5,IF(P5="",0,CHAR(39)&amp;P5&amp;CHAR(39)))&amp;"],"</f>
+        <v>['solar',8,10,'Solar Array','REPAIR',30,0,0,0,0,0,0,'upgrade1','reactor'],</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6">
-        <f>SUM(H6:L6)</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1213,19 +1276,19 @@
       <c r="J6">
         <v>20</v>
       </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="4"/>
+      <c r="O6" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q6" t="e">
-        <f>"["&amp;IF(ISNUMBER(C6),C6,IF(C6="",0,CHAR(39)&amp;C6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D6),D6,IF(D6="",0,CHAR(39)&amp;D6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E6),E6,IF(E6="",0,CHAR(39)&amp;E6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F6),F6,IF(F6="",0,CHAR(39)&amp;F6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G6),G6,IF(G6="",0,CHAR(39)&amp;G6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H6),H6,IF(H6="",0,CHAR(39)&amp;H6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I6),I6,IF(I6="",0,CHAR(39)&amp;I6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J6),J6,IF(J6="",0,CHAR(39)&amp;J6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K6),K6,IF(K6="",0,CHAR(39)&amp;K6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L6),L6,IF(L6="",0,CHAR(39)&amp;L6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M6),M6,IF(M6="",0,CHAR(39)&amp;M6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N6),N6,IF(N6="",0,CHAR(39)&amp;N6&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O6),O6,IF(O6="",0,CHAR(39)&amp;O6&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R6" t="str">
+        <f t="shared" si="2"/>
+        <v>['life',12,0,'Life Support','REPAIR',0,20,20,0,0,0,0,'base',0],</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7">
-        <f>SUM(H7:L7)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1246,22 +1309,22 @@
       <c r="I7">
         <v>30</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5" t="s">
+      <c r="N7" s="5"/>
+      <c r="O7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" t="e">
-        <f>"["&amp;IF(ISNUMBER(C7),C7,IF(C7="",0,CHAR(39)&amp;C7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D7),D7,IF(D7="",0,CHAR(39)&amp;D7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E7),E7,IF(E7="",0,CHAR(39)&amp;E7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F7),F7,IF(F7="",0,CHAR(39)&amp;F7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G7),G7,IF(G7="",0,CHAR(39)&amp;G7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H7),H7,IF(H7="",0,CHAR(39)&amp;H7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I7),I7,IF(I7="",0,CHAR(39)&amp;I7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J7),J7,IF(J7="",0,CHAR(39)&amp;J7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K7),K7,IF(K7="",0,CHAR(39)&amp;K7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L7),L7,IF(L7="",0,CHAR(39)&amp;L7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M7),M7,IF(M7="",0,CHAR(39)&amp;M7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N7),N7,IF(N7="",0,CHAR(39)&amp;N7&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O7),O7,IF(O7="",0,CHAR(39)&amp;O7&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R7" t="str">
+        <f t="shared" si="2"/>
+        <v>['water',6,10,'Water Recycler','REPAIR',0,30,0,0,0,0,0,'upgrade1','life'],</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8">
-        <f>SUM(H8:L8)</f>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1282,22 +1345,22 @@
       <c r="J8">
         <v>30</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5" t="s">
+      <c r="N8" s="5"/>
+      <c r="O8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" t="e">
-        <f>"["&amp;IF(ISNUMBER(C8),C8,IF(C8="",0,CHAR(39)&amp;C8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D8),D8,IF(D8="",0,CHAR(39)&amp;D8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E8),E8,IF(E8="",0,CHAR(39)&amp;E8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F8),F8,IF(F8="",0,CHAR(39)&amp;F8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G8),G8,IF(G8="",0,CHAR(39)&amp;G8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H8),H8,IF(H8="",0,CHAR(39)&amp;H8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I8),I8,IF(I8="",0,CHAR(39)&amp;I8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J8),J8,IF(J8="",0,CHAR(39)&amp;J8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K8),K8,IF(K8="",0,CHAR(39)&amp;K8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L8),L8,IF(L8="",0,CHAR(39)&amp;L8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M8),M8,IF(M8="",0,CHAR(39)&amp;M8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N8),N8,IF(N8="",0,CHAR(39)&amp;N8&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O8),O8,IF(O8="",0,CHAR(39)&amp;O8&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R8" t="str">
+        <f t="shared" si="2"/>
+        <v>['hydro',13,10,'Hydroponics','REPAIR',0,0,30,0,0,0,0,'upgrade1','life'],</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9">
-        <f>SUM(H9:L9)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1318,19 +1381,19 @@
       <c r="K9">
         <v>20</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="4"/>
+      <c r="O9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="Q9" t="e">
-        <f>"["&amp;IF(ISNUMBER(C9),C9,IF(C9="",0,CHAR(39)&amp;C9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D9),D9,IF(D9="",0,CHAR(39)&amp;D9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E9),E9,IF(E9="",0,CHAR(39)&amp;E9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F9),F9,IF(F9="",0,CHAR(39)&amp;F9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G9),G9,IF(G9="",0,CHAR(39)&amp;G9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H9),H9,IF(H9="",0,CHAR(39)&amp;H9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I9),I9,IF(I9="",0,CHAR(39)&amp;I9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J9),J9,IF(J9="",0,CHAR(39)&amp;J9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K9),K9,IF(K9="",0,CHAR(39)&amp;K9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L9),L9,IF(L9="",0,CHAR(39)&amp;L9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M9),M9,IF(M9="",0,CHAR(39)&amp;M9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N9),N9,IF(N9="",0,CHAR(39)&amp;N9&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O9),O9,IF(O9="",0,CHAR(39)&amp;O9&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R9" t="str">
+        <f t="shared" si="2"/>
+        <v>['cargo',4,0,'Cargo bay','REPAIR',0,0,0,20,0,0,0,'base',0],</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10">
-        <f>SUM(H10:L10)</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1351,22 +1414,22 @@
       <c r="K10">
         <v>50</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="5"/>
+      <c r="O10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" t="e">
-        <f>"["&amp;IF(ISNUMBER(C10),C10,IF(C10="",0,CHAR(39)&amp;C10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D10),D10,IF(D10="",0,CHAR(39)&amp;D10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E10),E10,IF(E10="",0,CHAR(39)&amp;E10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F10),F10,IF(F10="",0,CHAR(39)&amp;F10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G10),G10,IF(G10="",0,CHAR(39)&amp;G10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H10),H10,IF(H10="",0,CHAR(39)&amp;H10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I10),I10,IF(I10="",0,CHAR(39)&amp;I10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J10),J10,IF(J10="",0,CHAR(39)&amp;J10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K10),K10,IF(K10="",0,CHAR(39)&amp;K10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L10),L10,IF(L10="",0,CHAR(39)&amp;L10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M10),M10,IF(M10="",0,CHAR(39)&amp;M10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N10),N10,IF(N10="",0,CHAR(39)&amp;N10&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O10),O10,IF(O10="",0,CHAR(39)&amp;O10&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R10" t="str">
+        <f t="shared" si="2"/>
+        <v>['comms',11,10,'Comms array','REPAIR',0,0,0,50,0,0,0,'upgrade1','cargo'],</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11">
-        <f>SUM(H11:L11)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1387,22 +1450,22 @@
       <c r="K11">
         <v>10</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="6"/>
+      <c r="O11" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>5</v>
       </c>
-      <c r="Q11" t="e">
-        <f>"["&amp;IF(ISNUMBER(C11),C11,IF(C11="",0,CHAR(39)&amp;C11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D11),D11,IF(D11="",0,CHAR(39)&amp;D11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E11),E11,IF(E11="",0,CHAR(39)&amp;E11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F11),F11,IF(F11="",0,CHAR(39)&amp;F11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G11),G11,IF(G11="",0,CHAR(39)&amp;G11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H11),H11,IF(H11="",0,CHAR(39)&amp;H11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I11),I11,IF(I11="",0,CHAR(39)&amp;I11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J11),J11,IF(J11="",0,CHAR(39)&amp;J11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K11),K11,IF(K11="",0,CHAR(39)&amp;K11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L11),L11,IF(L11="",0,CHAR(39)&amp;L11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M11),M11,IF(M11="",0,CHAR(39)&amp;M11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N11),N11,IF(N11="",0,CHAR(39)&amp;N11&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O11),O11,IF(O11="",0,CHAR(39)&amp;O11&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R11" t="str">
+        <f t="shared" si="2"/>
+        <v>['fab',13,20,'Fabricator','REPAIR',0,0,0,10,0,0,0,'upgrade2','comms'],</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12">
-        <f>SUM(H12:L12)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1426,23 +1489,23 @@
       <c r="J12">
         <v>10</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="6"/>
+      <c r="O12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>135</v>
       </c>
-      <c r="Q12" t="e">
-        <f>"["&amp;IF(ISNUMBER(C12),C12,IF(C12="",0,CHAR(39)&amp;C12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D12),D12,IF(D12="",0,CHAR(39)&amp;D12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E12),E12,IF(E12="",0,CHAR(39)&amp;E12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F12),F12,IF(F12="",0,CHAR(39)&amp;F12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G12),G12,IF(G12="",0,CHAR(39)&amp;G12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H12),H12,IF(H12="",0,CHAR(39)&amp;H12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I12),I12,IF(I12="",0,CHAR(39)&amp;I12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J12),J12,IF(J12="",0,CHAR(39)&amp;J12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K12),K12,IF(K12="",0,CHAR(39)&amp;K12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L12),L12,IF(L12="",0,CHAR(39)&amp;L12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M12),M12,IF(M12="",0,CHAR(39)&amp;M12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N12),N12,IF(N12="",0,CHAR(39)&amp;N12&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O12),O12,IF(O12="",0,CHAR(39)&amp;O12&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R12" t="str">
+        <f t="shared" si="2"/>
+        <v>['med',14,20,'Medical bay','REPAIR',0,10,10,0,0,0,0,'upgrade2','water,hydro'],</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13">
-        <f>SUM(H13:L13)</f>
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
@@ -1459,30 +1522,27 @@
       <c r="G13" t="s">
         <v>38</v>
       </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
       <c r="L13">
         <v>1</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="6"/>
+      <c r="O13" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" t="e">
-        <f>"["&amp;IF(ISNUMBER(C13),C13,IF(C13="",0,CHAR(39)&amp;C13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D13),D13,IF(D13="",0,CHAR(39)&amp;D13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E13),E13,IF(E13="",0,CHAR(39)&amp;E13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F13),F13,IF(F13="",0,CHAR(39)&amp;F13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G13),G13,IF(G13="",0,CHAR(39)&amp;G13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H13),H13,IF(H13="",0,CHAR(39)&amp;H13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I13),I13,IF(I13="",0,CHAR(39)&amp;I13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J13),J13,IF(J13="",0,CHAR(39)&amp;J13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K13),K13,IF(K13="",0,CHAR(39)&amp;K13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L13),L13,IF(L13="",0,CHAR(39)&amp;L13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M13),M13,IF(M13="",0,CHAR(39)&amp;M13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N13),N13,IF(N13="",0,CHAR(39)&amp;N13&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O13),O13,IF(O13="",0,CHAR(39)&amp;O13&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R13" t="str">
+        <f t="shared" si="2"/>
+        <v>['anti',20,20,'Antimatter Chamber','REPAIR',0,0,0,0,1,0,0,'upgrade2','solar'],</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>63</v>
       </c>
       <c r="B14">
-        <f>SUM(H14:L14)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1497,24 +1557,24 @@
       <c r="G14" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>75</v>
       </c>
-      <c r="Q14" t="e">
-        <f>"["&amp;IF(ISNUMBER(C14),C14,IF(C14="",0,CHAR(39)&amp;C14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D14),D14,IF(D14="",0,CHAR(39)&amp;D14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E14),E14,IF(E14="",0,CHAR(39)&amp;E14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F14),F14,IF(F14="",0,CHAR(39)&amp;F14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G14),G14,IF(G14="",0,CHAR(39)&amp;G14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H14),H14,IF(H14="",0,CHAR(39)&amp;H14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I14),I14,IF(I14="",0,CHAR(39)&amp;I14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J14),J14,IF(J14="",0,CHAR(39)&amp;J14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K14),K14,IF(K14="",0,CHAR(39)&amp;K14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L14),L14,IF(L14="",0,CHAR(39)&amp;L14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M14),M14,IF(M14="",0,CHAR(39)&amp;M14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N14),N14,IF(N14="",0,CHAR(39)&amp;N14&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O14),O14,IF(O14="",0,CHAR(39)&amp;O14&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R14" t="str">
+        <f t="shared" si="2"/>
+        <v>['hazard',0,30,'Space Hazard Unit','REPAIR',0,0,0,0,0,0,'Allows you to explore space.','upgrade3','fab,med,anti'],</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="16"/>
       <c r="B15">
-        <f>SUM(H15:L15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1526,19 +1586,19 @@
       <c r="G15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="N15" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="N15" s="8"/>
-      <c r="Q15" t="e">
-        <f>"["&amp;IF(ISNUMBER(C15),C15,IF(C15="",0,CHAR(39)&amp;C15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D15),D15,IF(D15="",0,CHAR(39)&amp;D15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E15),E15,IF(E15="",0,CHAR(39)&amp;E15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F15),F15,IF(F15="",0,CHAR(39)&amp;F15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G15),G15,IF(G15="",0,CHAR(39)&amp;G15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H15),H15,IF(H15="",0,CHAR(39)&amp;H15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I15),I15,IF(I15="",0,CHAR(39)&amp;I15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J15),J15,IF(J15="",0,CHAR(39)&amp;J15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K15),K15,IF(K15="",0,CHAR(39)&amp;K15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L15),L15,IF(L15="",0,CHAR(39)&amp;L15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M15),M15,IF(M15="",0,CHAR(39)&amp;M15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N15),N15,IF(N15="",0,CHAR(39)&amp;N15&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O15),O15,IF(O15="",0,CHAR(39)&amp;O15&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O15" s="8"/>
+      <c r="R15" t="str">
+        <f t="shared" si="2"/>
+        <v>['obs',0,0,'Observatory','WORLDMAP',0,0,0,0,0,0,'Lets you peek into the endless void of space.',0,0],</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16"/>
       <c r="B16">
-        <f>SUM(H16:L16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1550,617 +1610,731 @@
       <c r="G16" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="N16" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="O16" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="Q16" t="e">
-        <f>"["&amp;IF(ISNUMBER(C16),C16,IF(C16="",0,CHAR(39)&amp;C16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D16),D16,IF(D16="",0,CHAR(39)&amp;D16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E16),E16,IF(E16="",0,CHAR(39)&amp;E16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F16),F16,IF(F16="",0,CHAR(39)&amp;F16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G16),G16,IF(G16="",0,CHAR(39)&amp;G16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H16),H16,IF(H16="",0,CHAR(39)&amp;H16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I16),I16,IF(I16="",0,CHAR(39)&amp;I16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J16),J16,IF(J16="",0,CHAR(39)&amp;J16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K16),K16,IF(K16="",0,CHAR(39)&amp;K16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L16),L16,IF(L16="",0,CHAR(39)&amp;L16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M16),M16,IF(M16="",0,CHAR(39)&amp;M16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N16),N16,IF(N16="",0,CHAR(39)&amp;N16&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O16),O16,IF(O16="",0,CHAR(39)&amp;O16&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R16" t="str">
+        <f t="shared" si="2"/>
+        <v>['shuttle',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,'Travel to new locations!','req hazard on homebase only',0],</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16"/>
       <c r="B17">
-        <f>SUM(H17:L17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="P17" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="2"/>
+        <v>['shuttleHome',0,0,'Shuttle bay','TRAVEL',0,0,0,0,0,0,'Travel to new locations!','will turn to shuttle','hazard'],</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="16"/>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="N18" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="N17" s="8"/>
-      <c r="Q17" t="e">
-        <f>"["&amp;IF(ISNUMBER(C17),C17,IF(C17="",0,CHAR(39)&amp;C17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D17),D17,IF(D17="",0,CHAR(39)&amp;D17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E17),E17,IF(E17="",0,CHAR(39)&amp;E17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F17),F17,IF(F17="",0,CHAR(39)&amp;F17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G17),G17,IF(G17="",0,CHAR(39)&amp;G17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H17),H17,IF(H17="",0,CHAR(39)&amp;H17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I17),I17,IF(I17="",0,CHAR(39)&amp;I17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J17),J17,IF(J17="",0,CHAR(39)&amp;J17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K17),K17,IF(K17="",0,CHAR(39)&amp;K17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L17),L17,IF(L17="",0,CHAR(39)&amp;L17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M17),M17,IF(M17="",0,CHAR(39)&amp;M17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N17),N17,IF(N17="",0,CHAR(39)&amp;N17&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O17),O17,IF(O17="",0,CHAR(39)&amp;O17&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="15"/>
-      <c r="B18">
-        <f>SUM(H18:L18)</f>
-        <v>120</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18">
-        <v>20</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18">
-        <v>120</v>
-      </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="Q18" t="e">
-        <f>"["&amp;IF(ISNUMBER(C18),C18,IF(C18="",0,CHAR(39)&amp;C18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D18),D18,IF(D18="",0,CHAR(39)&amp;D18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E18),E18,IF(E18="",0,CHAR(39)&amp;E18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F18),F18,IF(F18="",0,CHAR(39)&amp;F18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G18),G18,IF(G18="",0,CHAR(39)&amp;G18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H18),H18,IF(H18="",0,CHAR(39)&amp;H18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I18),I18,IF(I18="",0,CHAR(39)&amp;I18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J18),J18,IF(J18="",0,CHAR(39)&amp;J18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K18),K18,IF(K18="",0,CHAR(39)&amp;K18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L18),L18,IF(L18="",0,CHAR(39)&amp;L18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M18),M18,IF(M18="",0,CHAR(39)&amp;M18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N18),N18,IF(N18="",0,CHAR(39)&amp;N18&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O18),O18,IF(O18="",0,CHAR(39)&amp;O18&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O18" s="8"/>
+      <c r="R18" t="str">
+        <f t="shared" si="2"/>
+        <v>['upgrade',0,0,'Upgrade center','SEEUPGRADES',0,0,0,0,0,0,'See available upgrades.',0,0],</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="15"/>
       <c r="B19">
-        <f>SUM(H19:L19)</f>
-        <v>120</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="G19" t="s">
         <v>77</v>
       </c>
-      <c r="I19">
-        <v>120</v>
-      </c>
-      <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="Q19" t="e">
-        <f>"["&amp;IF(ISNUMBER(C19),C19,IF(C19="",0,CHAR(39)&amp;C19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D19),D19,IF(D19="",0,CHAR(39)&amp;D19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E19),E19,IF(E19="",0,CHAR(39)&amp;E19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F19),F19,IF(F19="",0,CHAR(39)&amp;F19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G19),G19,IF(G19="",0,CHAR(39)&amp;G19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H19),H19,IF(H19="",0,CHAR(39)&amp;H19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I19),I19,IF(I19="",0,CHAR(39)&amp;I19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J19),J19,IF(J19="",0,CHAR(39)&amp;J19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K19),K19,IF(K19="",0,CHAR(39)&amp;K19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L19),L19,IF(L19="",0,CHAR(39)&amp;L19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M19),M19,IF(M19="",0,CHAR(39)&amp;M19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N19),N19,IF(N19="",0,CHAR(39)&amp;N19&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O19),O19,IF(O19="",0,CHAR(39)&amp;O19&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O19" s="3"/>
+      <c r="R19" t="str">
+        <f t="shared" si="2"/>
+        <v>['custom',0,0,'$$$$$','CLAIM',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20">
-        <f>SUM(H20:L20)</f>
-        <v>120</v>
+        <f t="shared" ref="B20" si="3">SUM(H20:L20)</f>
+        <v>200</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E20">
         <v>20</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
         <v>77</v>
       </c>
-      <c r="J20">
-        <v>120</v>
-      </c>
-      <c r="M20" s="3"/>
+      <c r="H20">
+        <v>200</v>
+      </c>
       <c r="N20" s="3"/>
-      <c r="Q20" t="e">
-        <f>"["&amp;IF(ISNUMBER(C20),C20,IF(C20="",0,CHAR(39)&amp;C20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D20),D20,IF(D20="",0,CHAR(39)&amp;D20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E20),E20,IF(E20="",0,CHAR(39)&amp;E20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F20),F20,IF(F20="",0,CHAR(39)&amp;F20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G20),G20,IF(G20="",0,CHAR(39)&amp;G20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H20),H20,IF(H20="",0,CHAR(39)&amp;H20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I20),I20,IF(I20="",0,CHAR(39)&amp;I20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J20),J20,IF(J20="",0,CHAR(39)&amp;J20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K20),K20,IF(K20="",0,CHAR(39)&amp;K20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L20),L20,IF(L20="",0,CHAR(39)&amp;L20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M20),M20,IF(M20="",0,CHAR(39)&amp;M20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N20),N20,IF(N20="",0,CHAR(39)&amp;N20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O20),O20,IF(O20="",0,CHAR(39)&amp;O20&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O20" s="3"/>
+      <c r="R20" t="str">
+        <f t="shared" ref="R20" si="4">"["&amp;IF(ISNUMBER(C20),C20,IF(C20="",0,CHAR(39)&amp;C20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D20),D20,IF(D20="",0,CHAR(39)&amp;D20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E20),E20,IF(E20="",0,CHAR(39)&amp;E20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F20),F20,IF(F20="",0,CHAR(39)&amp;F20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G20),G20,IF(G20="",0,CHAR(39)&amp;G20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H20),H20,IF(H20="",0,CHAR(39)&amp;H20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I20),I20,IF(I20="",0,CHAR(39)&amp;I20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J20),J20,IF(J20="",0,CHAR(39)&amp;J20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K20),K20,IF(K20="",0,CHAR(39)&amp;K20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L20),L20,IF(L20="",0,CHAR(39)&amp;L20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M20),M20,IF(M20="",0,CHAR(39)&amp;M20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N20),N20,IF(N20="",0,CHAR(39)&amp;N20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O20),O20,IF(O20="",0,CHAR(39)&amp;O20&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(P20),P20,IF(P20="",0,CHAR(39)&amp;P20&amp;CHAR(39)))&amp;"],"</f>
+        <v>['chestenergy',0,20,'Energy cells','CLAIM',200,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
       <c r="B21">
-        <f>SUM(H21:L21)</f>
-        <v>120</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E21">
         <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s">
         <v>77</v>
       </c>
-      <c r="K21">
-        <v>120</v>
-      </c>
-      <c r="M21" s="3"/>
+      <c r="I21">
+        <v>200</v>
+      </c>
       <c r="N21" s="3"/>
-      <c r="Q21" t="e">
-        <f>"["&amp;IF(ISNUMBER(C21),C21,IF(C21="",0,CHAR(39)&amp;C21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D21),D21,IF(D21="",0,CHAR(39)&amp;D21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E21),E21,IF(E21="",0,CHAR(39)&amp;E21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F21),F21,IF(F21="",0,CHAR(39)&amp;F21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G21),G21,IF(G21="",0,CHAR(39)&amp;G21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H21),H21,IF(H21="",0,CHAR(39)&amp;H21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I21),I21,IF(I21="",0,CHAR(39)&amp;I21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J21),J21,IF(J21="",0,CHAR(39)&amp;J21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K21),K21,IF(K21="",0,CHAR(39)&amp;K21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L21),L21,IF(L21="",0,CHAR(39)&amp;L21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M21),M21,IF(M21="",0,CHAR(39)&amp;M21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N21),N21,IF(N21="",0,CHAR(39)&amp;N21&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O21),O21,IF(O21="",0,CHAR(39)&amp;O21&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O21" s="3"/>
+      <c r="R21" t="str">
+        <f t="shared" si="2"/>
+        <v>['chestwater',0,20,'Ice blocks','CLAIM',0,200,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22">
-        <f>SUM(H22:L22)</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
         <v>77</v>
       </c>
-      <c r="H22">
-        <v>10</v>
-      </c>
-      <c r="M22" s="3"/>
+      <c r="J22">
+        <v>200</v>
+      </c>
       <c r="N22" s="3"/>
-      <c r="Q22" t="e">
-        <f>"["&amp;IF(ISNUMBER(C22),C22,IF(C22="",0,CHAR(39)&amp;C22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D22),D22,IF(D22="",0,CHAR(39)&amp;D22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E22),E22,IF(E22="",0,CHAR(39)&amp;E22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F22),F22,IF(F22="",0,CHAR(39)&amp;F22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G22),G22,IF(G22="",0,CHAR(39)&amp;G22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H22),H22,IF(H22="",0,CHAR(39)&amp;H22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I22),I22,IF(I22="",0,CHAR(39)&amp;I22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J22),J22,IF(J22="",0,CHAR(39)&amp;J22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K22),K22,IF(K22="",0,CHAR(39)&amp;K22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L22),L22,IF(L22="",0,CHAR(39)&amp;L22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M22),M22,IF(M22="",0,CHAR(39)&amp;M22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N22),N22,IF(N22="",0,CHAR(39)&amp;N22&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O22),O22,IF(O22="",0,CHAR(39)&amp;O22&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O22" s="3"/>
+      <c r="R22" t="str">
+        <f t="shared" si="2"/>
+        <v>['chestfood',0,20,'Nutrient packs','CLAIM',0,0,200,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="15"/>
       <c r="B23">
-        <f>SUM(H23:L23)</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
         <v>77</v>
       </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="M23" s="3"/>
+      <c r="K23">
+        <v>200</v>
+      </c>
       <c r="N23" s="3"/>
-      <c r="Q23" t="e">
-        <f>"["&amp;IF(ISNUMBER(C23),C23,IF(C23="",0,CHAR(39)&amp;C23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D23),D23,IF(D23="",0,CHAR(39)&amp;D23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E23),E23,IF(E23="",0,CHAR(39)&amp;E23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F23),F23,IF(F23="",0,CHAR(39)&amp;F23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G23),G23,IF(G23="",0,CHAR(39)&amp;G23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H23),H23,IF(H23="",0,CHAR(39)&amp;H23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I23),I23,IF(I23="",0,CHAR(39)&amp;I23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J23),J23,IF(J23="",0,CHAR(39)&amp;J23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K23),K23,IF(K23="",0,CHAR(39)&amp;K23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L23),L23,IF(L23="",0,CHAR(39)&amp;L23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M23),M23,IF(M23="",0,CHAR(39)&amp;M23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N23),N23,IF(N23="",0,CHAR(39)&amp;N23&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O23),O23,IF(O23="",0,CHAR(39)&amp;O23&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O23" s="3"/>
+      <c r="R23" t="str">
+        <f t="shared" si="2"/>
+        <v>['chestparts',0,20,'Parts box','CLAIM',0,0,0,200,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24">
-        <f>SUM(H24:L24)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
         <v>77</v>
       </c>
-      <c r="J24">
-        <v>10</v>
-      </c>
-      <c r="M24" s="3"/>
+      <c r="H24">
+        <v>10</v>
+      </c>
       <c r="N24" s="3"/>
-      <c r="Q24" t="e">
-        <f>"["&amp;IF(ISNUMBER(C24),C24,IF(C24="",0,CHAR(39)&amp;C24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D24),D24,IF(D24="",0,CHAR(39)&amp;D24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E24),E24,IF(E24="",0,CHAR(39)&amp;E24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F24),F24,IF(F24="",0,CHAR(39)&amp;F24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G24),G24,IF(G24="",0,CHAR(39)&amp;G24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H24),H24,IF(H24="",0,CHAR(39)&amp;H24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I24),I24,IF(I24="",0,CHAR(39)&amp;I24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J24),J24,IF(J24="",0,CHAR(39)&amp;J24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K24),K24,IF(K24="",0,CHAR(39)&amp;K24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L24),L24,IF(L24="",0,CHAR(39)&amp;L24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M24),M24,IF(M24="",0,CHAR(39)&amp;M24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N24),N24,IF(N24="",0,CHAR(39)&amp;N24&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O24),O24,IF(O24="",0,CHAR(39)&amp;O24&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O24" s="3"/>
+      <c r="R24" t="str">
+        <f t="shared" si="2"/>
+        <v>['smallenergy',0,0,'Small battery','CLAIM',10,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="15"/>
       <c r="B25">
-        <f>SUM(H25:L25)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G25" t="s">
         <v>77</v>
       </c>
-      <c r="K25">
-        <v>10</v>
-      </c>
-      <c r="M25" s="3"/>
+      <c r="I25">
+        <v>10</v>
+      </c>
       <c r="N25" s="3"/>
-      <c r="Q25" t="e">
-        <f>"["&amp;IF(ISNUMBER(C25),C25,IF(C25="",0,CHAR(39)&amp;C25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D25),D25,IF(D25="",0,CHAR(39)&amp;D25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E25),E25,IF(E25="",0,CHAR(39)&amp;E25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F25),F25,IF(F25="",0,CHAR(39)&amp;F25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G25),G25,IF(G25="",0,CHAR(39)&amp;G25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H25),H25,IF(H25="",0,CHAR(39)&amp;H25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I25),I25,IF(I25="",0,CHAR(39)&amp;I25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J25),J25,IF(J25="",0,CHAR(39)&amp;J25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K25),K25,IF(K25="",0,CHAR(39)&amp;K25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L25),L25,IF(L25="",0,CHAR(39)&amp;L25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M25),M25,IF(M25="",0,CHAR(39)&amp;M25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N25),N25,IF(N25="",0,CHAR(39)&amp;N25&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O25),O25,IF(O25="",0,CHAR(39)&amp;O25&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O25" s="3"/>
+      <c r="R25" t="str">
+        <f t="shared" si="2"/>
+        <v>['smallwater',0,0,'Small water bottle','CLAIM',0,10,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26">
-        <f>SUM(H26:L26)</f>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E26">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="G26" t="s">
         <v>77</v>
       </c>
-      <c r="L26">
-        <v>80</v>
-      </c>
-      <c r="M26" s="3"/>
+      <c r="J26">
+        <v>10</v>
+      </c>
       <c r="N26" s="3"/>
-      <c r="Q26" t="e">
-        <f>"["&amp;IF(ISNUMBER(C26),C26,IF(C26="",0,CHAR(39)&amp;C26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D26),D26,IF(D26="",0,CHAR(39)&amp;D26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E26),E26,IF(E26="",0,CHAR(39)&amp;E26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F26),F26,IF(F26="",0,CHAR(39)&amp;F26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G26),G26,IF(G26="",0,CHAR(39)&amp;G26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H26),H26,IF(H26="",0,CHAR(39)&amp;H26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I26),I26,IF(I26="",0,CHAR(39)&amp;I26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J26),J26,IF(J26="",0,CHAR(39)&amp;J26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K26),K26,IF(K26="",0,CHAR(39)&amp;K26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L26),L26,IF(L26="",0,CHAR(39)&amp;L26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M26),M26,IF(M26="",0,CHAR(39)&amp;M26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N26),N26,IF(N26="",0,CHAR(39)&amp;N26&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O26),O26,IF(O26="",0,CHAR(39)&amp;O26&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O26" s="3"/>
+      <c r="R26" t="str">
+        <f t="shared" si="2"/>
+        <v>['smallfood',0,0,'Small candy bar','CLAIM',0,0,10,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="15"/>
       <c r="B27">
-        <f>SUM(H27:L27)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
-      </c>
-      <c r="M27" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
       <c r="N27" s="3"/>
-      <c r="Q27" t="e">
-        <f>"["&amp;IF(ISNUMBER(C27),C27,IF(C27="",0,CHAR(39)&amp;C27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D27),D27,IF(D27="",0,CHAR(39)&amp;D27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E27),E27,IF(E27="",0,CHAR(39)&amp;E27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F27),F27,IF(F27="",0,CHAR(39)&amp;F27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G27),G27,IF(G27="",0,CHAR(39)&amp;G27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H27),H27,IF(H27="",0,CHAR(39)&amp;H27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I27),I27,IF(I27="",0,CHAR(39)&amp;I27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J27),J27,IF(J27="",0,CHAR(39)&amp;J27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K27),K27,IF(K27="",0,CHAR(39)&amp;K27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L27),L27,IF(L27="",0,CHAR(39)&amp;L27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M27),M27,IF(M27="",0,CHAR(39)&amp;M27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N27),N27,IF(N27="",0,CHAR(39)&amp;N27&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O27),O27,IF(O27="",0,CHAR(39)&amp;O27&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O27" s="3"/>
+      <c r="R27" t="str">
+        <f t="shared" si="2"/>
+        <v>['smallparts',0,0,'Small circuits','CLAIM',0,0,0,10,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28">
-        <f>SUM(H28:L28)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
-      </c>
-      <c r="M28" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="L28">
+        <v>3</v>
+      </c>
       <c r="N28" s="3"/>
-      <c r="Q28" t="e">
-        <f>"["&amp;IF(ISNUMBER(C28),C28,IF(C28="",0,CHAR(39)&amp;C28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D28),D28,IF(D28="",0,CHAR(39)&amp;D28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E28),E28,IF(E28="",0,CHAR(39)&amp;E28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F28),F28,IF(F28="",0,CHAR(39)&amp;F28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G28),G28,IF(G28="",0,CHAR(39)&amp;G28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H28),H28,IF(H28="",0,CHAR(39)&amp;H28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I28),I28,IF(I28="",0,CHAR(39)&amp;I28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J28),J28,IF(J28="",0,CHAR(39)&amp;J28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K28),K28,IF(K28="",0,CHAR(39)&amp;K28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L28),L28,IF(L28="",0,CHAR(39)&amp;L28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M28),M28,IF(M28="",0,CHAR(39)&amp;M28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N28),N28,IF(N28="",0,CHAR(39)&amp;N28&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O28),O28,IF(O28="",0,CHAR(39)&amp;O28&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O28" s="3"/>
+      <c r="R28" t="str">
+        <f t="shared" si="2"/>
+        <v>['anti3',0,30,'Antimatter traces','CLAIM',0,0,0,0,3,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="15"/>
       <c r="B29">
-        <f>SUM(H29:L29)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="E29">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="G29" t="s">
-        <v>95</v>
-      </c>
-      <c r="M29" s="3"/>
+        <v>77</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
       <c r="N29" s="3"/>
-      <c r="Q29" t="e">
-        <f>"["&amp;IF(ISNUMBER(C29),C29,IF(C29="",0,CHAR(39)&amp;C29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D29),D29,IF(D29="",0,CHAR(39)&amp;D29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E29),E29,IF(E29="",0,CHAR(39)&amp;E29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F29),F29,IF(F29="",0,CHAR(39)&amp;F29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G29),G29,IF(G29="",0,CHAR(39)&amp;G29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H29),H29,IF(H29="",0,CHAR(39)&amp;H29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I29),I29,IF(I29="",0,CHAR(39)&amp;I29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J29),J29,IF(J29="",0,CHAR(39)&amp;J29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K29),K29,IF(K29="",0,CHAR(39)&amp;K29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L29),L29,IF(L29="",0,CHAR(39)&amp;L29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M29),M29,IF(M29="",0,CHAR(39)&amp;M29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N29),N29,IF(N29="",0,CHAR(39)&amp;N29&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O29),O29,IF(O29="",0,CHAR(39)&amp;O29&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O29" s="3"/>
+      <c r="R29" t="str">
+        <f t="shared" si="2"/>
+        <v>['anti5',0,40,'Antimatter residue','CLAIM',0,0,0,0,5,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30">
-        <f>SUM(H30:L30)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30">
+        <v>50</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" t="s">
+        <v>77</v>
+      </c>
+      <c r="L30">
+        <v>8</v>
+      </c>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="R30" t="str">
+        <f t="shared" si="2"/>
+        <v>['anti8',0,50,'Antimatter vein','CLAIM',0,0,0,0,8,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="B31">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G31" t="s">
+        <v>77</v>
+      </c>
+      <c r="L31">
+        <v>10</v>
+      </c>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="R31" t="str">
+        <f t="shared" si="2"/>
+        <v>['anti10',0,60,'Antimatter deposit','CLAIM',0,0,0,0,10,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="B32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s">
+        <v>95</v>
+      </c>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="R32" t="str">
+        <f t="shared" si="2"/>
+        <v>['door_easy',0,0,'Damaged door','HACK',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="B33">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33">
+        <v>20</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" t="s">
+        <v>95</v>
+      </c>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="R33" t="str">
+        <f t="shared" si="2"/>
+        <v>['door_medium',0,20,'Locked door','HACK',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="15"/>
+      <c r="B34">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34">
+        <v>50</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" t="s">
+        <v>95</v>
+      </c>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="R34" t="str">
+        <f t="shared" si="2"/>
+        <v>['door_hard',0,50,'Reinforced door','HACK',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="B35">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E30">
+      <c r="E35">
         <v>70</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G35" t="s">
         <v>95</v>
       </c>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="Q30" t="e">
-        <f>"["&amp;IF(ISNUMBER(C30),C30,IF(C30="",0,CHAR(39)&amp;C30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D30),D30,IF(D30="",0,CHAR(39)&amp;D30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E30),E30,IF(E30="",0,CHAR(39)&amp;E30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F30),F30,IF(F30="",0,CHAR(39)&amp;F30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G30),G30,IF(G30="",0,CHAR(39)&amp;G30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H30),H30,IF(H30="",0,CHAR(39)&amp;H30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I30),I30,IF(I30="",0,CHAR(39)&amp;I30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J30),J30,IF(J30="",0,CHAR(39)&amp;J30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K30),K30,IF(K30="",0,CHAR(39)&amp;K30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L30),L30,IF(L30="",0,CHAR(39)&amp;L30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M30),M30,IF(M30="",0,CHAR(39)&amp;M30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N30),N30,IF(N30="",0,CHAR(39)&amp;N30&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O30),O30,IF(O30="",0,CHAR(39)&amp;O30&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31" s="13" t="s">
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="R35" t="str">
+        <f t="shared" si="2"/>
+        <v>['door_extreme',0,70,'High security door','HACK',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B31">
-        <f>SUM(H31:L31)</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="B36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E31">
-        <v>10</v>
-      </c>
-      <c r="F31" s="9" t="s">
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="G31" t="s">
-        <v>96</v>
-      </c>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="Q31" t="e">
-        <f>"["&amp;IF(ISNUMBER(C31),C31,IF(C31="",0,CHAR(39)&amp;C31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D31),D31,IF(D31="",0,CHAR(39)&amp;D31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E31),E31,IF(E31="",0,CHAR(39)&amp;E31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F31),F31,IF(F31="",0,CHAR(39)&amp;F31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G31),G31,IF(G31="",0,CHAR(39)&amp;G31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H31),H31,IF(H31="",0,CHAR(39)&amp;H31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I31),I31,IF(I31="",0,CHAR(39)&amp;I31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J31),J31,IF(J31="",0,CHAR(39)&amp;J31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K31),K31,IF(K31="",0,CHAR(39)&amp;K31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L31),L31,IF(L31="",0,CHAR(39)&amp;L31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M31),M31,IF(M31="",0,CHAR(39)&amp;M31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N31),N31,IF(N31="",0,CHAR(39)&amp;N31&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O31),O31,IF(O31="",0,CHAR(39)&amp;O31&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32">
-        <f>SUM(H32:L32)</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32">
-        <v>10</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" t="s">
-        <v>96</v>
-      </c>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="Q32" t="e">
-        <f>"["&amp;IF(ISNUMBER(C32),C32,IF(C32="",0,CHAR(39)&amp;C32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D32),D32,IF(D32="",0,CHAR(39)&amp;D32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E32),E32,IF(E32="",0,CHAR(39)&amp;E32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F32),F32,IF(F32="",0,CHAR(39)&amp;F32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G32),G32,IF(G32="",0,CHAR(39)&amp;G32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H32),H32,IF(H32="",0,CHAR(39)&amp;H32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I32),I32,IF(I32="",0,CHAR(39)&amp;I32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J32),J32,IF(J32="",0,CHAR(39)&amp;J32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K32),K32,IF(K32="",0,CHAR(39)&amp;K32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L32),L32,IF(L32="",0,CHAR(39)&amp;L32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M32),M32,IF(M32="",0,CHAR(39)&amp;M32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(N32),N32,IF(N32="",0,CHAR(39)&amp;N32&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(O32),O32,IF(O32="",0,CHAR(39)&amp;O32&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33">
-        <f>SUM(H33:L33)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E33">
-        <v>10</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G33" t="s">
-        <v>96</v>
-      </c>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="Q33" t="e">
-        <f>"["&amp;IF(ISNUMBER(C33),C33,IF(C33="",0,CHAR(39)&amp;C33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D33),D33,IF(D33="",0,CHAR(39)&amp;D33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E33),E33,IF(E33="",0,CHAR(39)&amp;E33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F33),F33,IF(F33="",0,CHAR(39)&amp;F33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G33),G33,IF(G33="",0,CHAR(39)&amp;G33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H33),H33,IF(H33="",0,CHAR(39)&amp;H33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I33),I33,IF(I33="",0,CHAR(39)&amp;I33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J33),J33,IF(J33="",0,CHAR(39)&amp;J33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K33),K33,IF(K33="",0,CHAR(39)&amp;K33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L33),L33,IF(L33="",0,CHAR(39)&amp;L33&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M33),M33,IF(M33="",0,CHAR(39)&amp;M33&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34">
-        <f>SUM(H34:L34)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34">
-        <v>10</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G34" t="s">
-        <v>96</v>
-      </c>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-      <c r="Q34" t="e">
-        <f>"["&amp;IF(ISNUMBER(C34),C34,IF(C34="",0,CHAR(39)&amp;C34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D34),D34,IF(D34="",0,CHAR(39)&amp;D34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E34),E34,IF(E34="",0,CHAR(39)&amp;E34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F34),F34,IF(F34="",0,CHAR(39)&amp;F34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G34),G34,IF(G34="",0,CHAR(39)&amp;G34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H34),H34,IF(H34="",0,CHAR(39)&amp;H34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I34),I34,IF(I34="",0,CHAR(39)&amp;I34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J34),J34,IF(J34="",0,CHAR(39)&amp;J34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K34),K34,IF(K34="",0,CHAR(39)&amp;K34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L34),L34,IF(L34="",0,CHAR(39)&amp;L34&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M34),M34,IF(M34="",0,CHAR(39)&amp;M34&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35">
-        <f>SUM(H35:L35)</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35">
-        <v>10</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="G35" t="s">
-        <v>96</v>
-      </c>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-      <c r="Q35" t="e">
-        <f>"["&amp;IF(ISNUMBER(C35),C35,IF(C35="",0,CHAR(39)&amp;C35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D35),D35,IF(D35="",0,CHAR(39)&amp;D35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E35),E35,IF(E35="",0,CHAR(39)&amp;E35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F35),F35,IF(F35="",0,CHAR(39)&amp;F35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G35),G35,IF(G35="",0,CHAR(39)&amp;G35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H35),H35,IF(H35="",0,CHAR(39)&amp;H35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I35),I35,IF(I35="",0,CHAR(39)&amp;I35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J35),J35,IF(J35="",0,CHAR(39)&amp;J35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K35),K35,IF(K35="",0,CHAR(39)&amp;K35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L35),L35,IF(L35="",0,CHAR(39)&amp;L35&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M35),M35,IF(M35="",0,CHAR(39)&amp;M35&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36">
-        <f>SUM(H36:L36)</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="E36">
-        <v>10</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>134</v>
       </c>
       <c r="G36" t="s">
         <v>96</v>
       </c>
-      <c r="M36" s="9"/>
       <c r="N36" s="9"/>
-      <c r="Q36" t="e">
-        <f>"["&amp;IF(ISNUMBER(C36),C36,IF(C36="",0,CHAR(39)&amp;C36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D36),D36,IF(D36="",0,CHAR(39)&amp;D36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E36),E36,IF(E36="",0,CHAR(39)&amp;E36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F36),F36,IF(F36="",0,CHAR(39)&amp;F36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G36),G36,IF(G36="",0,CHAR(39)&amp;G36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H36),H36,IF(H36="",0,CHAR(39)&amp;H36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I36),I36,IF(I36="",0,CHAR(39)&amp;I36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J36),J36,IF(J36="",0,CHAR(39)&amp;J36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K36),K36,IF(K36="",0,CHAR(39)&amp;K36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L36),L36,IF(L36="",0,CHAR(39)&amp;L36&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M36),M36,IF(M36="",0,CHAR(39)&amp;M36&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O36" s="9"/>
+      <c r="R36" t="str">
+        <f t="shared" si="2"/>
+        <v>['plants',0,10,'Plants','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37">
-        <f>SUM(H37:L37)</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="F37" s="9"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="G37" t="s">
         <v>96</v>
       </c>
-      <c r="M37" s="9"/>
       <c r="N37" s="9"/>
-      <c r="Q37" t="e">
-        <f>"["&amp;IF(ISNUMBER(C37),C37,IF(C37="",0,CHAR(39)&amp;C37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D37),D37,IF(D37="",0,CHAR(39)&amp;D37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E37),E37,IF(E37="",0,CHAR(39)&amp;E37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F37),F37,IF(F37="",0,CHAR(39)&amp;F37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G37),G37,IF(G37="",0,CHAR(39)&amp;G37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H37),H37,IF(H37="",0,CHAR(39)&amp;H37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I37),I37,IF(I37="",0,CHAR(39)&amp;I37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J37),J37,IF(J37="",0,CHAR(39)&amp;J37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K37),K37,IF(K37="",0,CHAR(39)&amp;K37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L37),L37,IF(L37="",0,CHAR(39)&amp;L37&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M37),M37,IF(M37="",0,CHAR(39)&amp;M37&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O37" s="9"/>
+      <c r="R37" t="str">
+        <f t="shared" si="2"/>
+        <v>['fridge',0,10,'Fridge','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38">
-        <f>SUM(H38:L38)</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="F38" s="9"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>128</v>
+      </c>
       <c r="G38" t="s">
         <v>96</v>
       </c>
-      <c r="M38" s="9"/>
       <c r="N38" s="9"/>
-      <c r="Q38" t="e">
-        <f>"["&amp;IF(ISNUMBER(C38),C38,IF(C38="",0,CHAR(39)&amp;C38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(D38),D38,IF(D38="",0,CHAR(39)&amp;D38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(E38),E38,IF(E38="",0,CHAR(39)&amp;E38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(F38),F38,IF(F38="",0,CHAR(39)&amp;F38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(G38),G38,IF(G38="",0,CHAR(39)&amp;G38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(H38),H38,IF(H38="",0,CHAR(39)&amp;H38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(I38),I38,IF(I38="",0,CHAR(39)&amp;I38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(J38),J38,IF(J38="",0,CHAR(39)&amp;J38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(K38),K38,IF(K38="",0,CHAR(39)&amp;K38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(L38),L38,IF(L38="",0,CHAR(39)&amp;L38&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(#REF!),#REF!,IF(#REF!="",0,CHAR(39)&amp;#REF!&amp;CHAR(39)))&amp;","&amp;IF(ISNUMBER(M38),M38,IF(M38="",0,CHAR(39)&amp;M38&amp;CHAR(39)))&amp;"],"</f>
-        <v>#REF!</v>
+      <c r="O38" s="9"/>
+      <c r="R38" t="str">
+        <f t="shared" si="2"/>
+        <v>['sink',0,10,'Sink','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="G39" t="s">
+        <v>96</v>
+      </c>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="R39" t="str">
+        <f t="shared" si="2"/>
+        <v>['shower',0,10,'Shower','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" s="13"/>
+      <c r="B40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="G40" t="s">
+        <v>96</v>
+      </c>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="R40" t="str">
+        <f t="shared" si="2"/>
+        <v>['sofa',0,10,'Sofa','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G41" t="s">
+        <v>96</v>
+      </c>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="R41" t="str">
+        <f t="shared" si="2"/>
+        <v>['table',0,10,'Table','RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" t="s">
+        <v>96</v>
+      </c>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="R42" t="str">
+        <f t="shared" si="2"/>
+        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" t="s">
+        <v>96</v>
+      </c>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="R43" t="str">
+        <f t="shared" si="2"/>
+        <v>[0,0,0,0,'RESTORE',0,0,0,0,0,0,0,0,0],</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="A36:A43"/>
     <mergeCell ref="H1:K1"/>
     <mergeCell ref="A4:A13"/>
-    <mergeCell ref="A18:A30"/>
-    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A19:A35"/>
+    <mergeCell ref="A14:A18"/>
   </mergeCells>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C1048576 C1:C17">
+  <conditionalFormatting sqref="C36:C1048576 C1:C18">
     <cfRule type="duplicateValues" dxfId="10" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:R2 D2:L2">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F31:F38">
-    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M2">
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M31:N38">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:O3">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:P2">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E56">
+  <conditionalFormatting sqref="E4:E61">
     <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
@@ -2172,25 +2346,46 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F36:F43">
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N36:O43">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:P3">
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:Q2">
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:S2 D2:M2">
+    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="97.453125" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="97.44140625" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="97.453125" style="10"/>
+    <col min="1" max="16384" width="97.44140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>108</v>
       </c>
@@ -2201,17 +2396,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:Z31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="6" width="7.36328125" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" customWidth="1"/>
+    <col min="5" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:26" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -2283,7 +2478,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -2331,7 +2526,7 @@
         <v>["terminal","delay","question","pretty","action","energy","food","water","parts","metals","titanium","alloy"],</v>
       </c>
     </row>
-    <row r="4" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B4">
         <f>SUM(E4:AA4)</f>
         <v>55</v>
@@ -2363,7 +2558,7 @@
         <v>["reactor",15,0,"Reactor","REPAIR",40,0,0,0,0,0,0],</v>
       </c>
     </row>
-    <row r="5" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B5">
         <f t="shared" ref="B5:B31" si="1">SUM(E5:AA5)</f>
         <v>55</v>
@@ -2399,7 +2594,7 @@
         <v xml:space="preserve"> * @property {number} solar</v>
       </c>
     </row>
-    <row r="6" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B6">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -2438,7 +2633,7 @@
         <v xml:space="preserve"> * @property {number} hydro</v>
       </c>
     </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B7">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2474,7 +2669,7 @@
         <v xml:space="preserve"> * @property {number} water</v>
       </c>
     </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B8">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -2513,7 +2708,7 @@
         <v xml:space="preserve"> * @property {number} cargo</v>
       </c>
     </row>
-    <row r="9" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B9">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -2549,7 +2744,7 @@
         <v xml:space="preserve"> * @property {number} comms</v>
       </c>
     </row>
-    <row r="10" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B10">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -2588,7 +2783,7 @@
         <v xml:space="preserve"> * @property {number} fab</v>
       </c>
     </row>
-    <row r="11" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B11">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -2624,7 +2819,7 @@
         <v xml:space="preserve"> * @property {number} med</v>
       </c>
     </row>
-    <row r="12" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B12">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -2663,7 +2858,7 @@
         <v xml:space="preserve"> * @property {number} life</v>
       </c>
     </row>
-    <row r="13" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:26" x14ac:dyDescent="0.3">
       <c r="B13">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -2699,7 +2894,7 @@
         <v xml:space="preserve"> * @property {number} machine</v>
       </c>
     </row>
-    <row r="14" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C14" t="str">
         <f t="shared" si="2"/>
         <v>s</v>
@@ -2722,7 +2917,7 @@
         <v xml:space="preserve"> * @property {number} shuttle</v>
       </c>
     </row>
-    <row r="15" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f t="shared" si="2"/>
         <v>a</v>
@@ -2745,7 +2940,7 @@
         <v xml:space="preserve"> * @property {number} access</v>
       </c>
     </row>
-    <row r="16" spans="2:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:26" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f t="shared" si="2"/>
         <v>d</v>
@@ -2768,7 +2963,7 @@
         <v xml:space="preserve"> * @property {number} door</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -2810,7 +3005,7 @@
         <v xml:space="preserve"> * @property {number} mining</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -2849,7 +3044,7 @@
         <v xml:space="preserve"> * @property {number} scrapyard</v>
       </c>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -2894,7 +3089,7 @@
         <v xml:space="preserve"> * @property {number} data</v>
       </c>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -2936,7 +3131,7 @@
         <v xml:space="preserve"> * @property {number} supply</v>
       </c>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21">
         <f t="shared" si="1"/>
         <v>140</v>
@@ -2978,7 +3173,7 @@
         <v xml:space="preserve"> * @property {number} fusion</v>
       </c>
     </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22">
         <f t="shared" si="1"/>
         <v>170</v>
@@ -3017,7 +3212,7 @@
         <v xml:space="preserve"> * @property {number} alloy</v>
       </c>
     </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -3059,7 +3254,7 @@
         <v xml:space="preserve"> * @property {number} research</v>
       </c>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3069,7 +3264,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3079,7 +3274,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3089,7 +3284,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3099,7 +3294,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3109,7 +3304,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3119,7 +3314,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -3129,7 +3324,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B31">
         <f t="shared" si="1"/>
         <v>0</v>
